--- a/ΟΒΙΒv2.2/Biobank, Collection, Network, Research Resource(v2.2).xlsx
+++ b/ΟΒΙΒv2.2/Biobank, Collection, Network, Research Resource(v2.2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12048" windowHeight="9048" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="sample,sample donor,event(v2.1)" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="707">
   <si>
     <t>Entity</t>
   </si>
@@ -2346,12 +2346,6 @@
     <t>has age unit</t>
   </si>
   <si>
-    <t>http://purl.obolibrary.org/obo/OBIB_0000671</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/OBIB_0000672</t>
-  </si>
-  <si>
     <t>http://purl.obolibrary.org/obo/OBIB_0002036</t>
   </si>
   <si>
@@ -2416,6 +2410,24 @@
   </si>
   <si>
     <t xml:space="preserve">is associated with </t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002073</t>
+  </si>
+  <si>
+    <t>collection</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection </t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/RO_0002350</t>
+  </si>
+  <si>
+    <t>member of</t>
   </si>
 </sst>
 </file>
@@ -2759,7 +2771,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2782,6 +2794,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2854,7 +2872,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2994,6 +3012,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5341,7 +5360,7 @@
     <col min="9" max="9" width="51.5546875" customWidth="1"/>
     <col min="10" max="10" width="74.44140625" customWidth="1"/>
     <col min="11" max="11" width="100.33203125" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="46.33203125" customWidth="1"/>
     <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7224,7 +7243,7 @@
       <c r="K51" s="38" t="s">
         <v>558</v>
       </c>
-      <c r="L51" s="32" t="s">
+      <c r="L51" s="77" t="s">
         <v>559</v>
       </c>
       <c r="M51" s="32"/>
@@ -8540,14 +8559,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.77734375" customWidth="1"/>
     <col min="2" max="2" width="39.44140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" customWidth="1"/>
     <col min="6" max="6" width="39.44140625" style="1" customWidth="1"/>
     <col min="11" max="11" width="20.88671875" customWidth="1"/>
     <col min="12" max="12" width="41.6640625" style="47" customWidth="1"/>
@@ -8653,10 +8672,10 @@
         <v>280</v>
       </c>
       <c r="C6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E6" t="s">
         <v>663</v>
@@ -8674,10 +8693,10 @@
         <v>662</v>
       </c>
       <c r="C7" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>291</v>
@@ -8695,10 +8714,10 @@
         <v>662</v>
       </c>
       <c r="C8" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E8" s="32" t="s">
         <v>299</v>
@@ -8716,10 +8735,10 @@
         <v>662</v>
       </c>
       <c r="C9" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E9" s="32" t="s">
         <v>307</v>
@@ -8737,10 +8756,10 @@
         <v>314</v>
       </c>
       <c r="C10" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E10" t="s">
         <v>663</v>
@@ -8751,475 +8770,474 @@
       <c r="L10" s="52"/>
     </row>
     <row r="11" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
+      <c r="A11" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C11" t="s">
+        <v>706</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>481</v>
+      </c>
       <c r="L11" s="52"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="32"/>
+      <c r="L12" s="52"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
         <v>318</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>320</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C13" t="s">
-        <v>199</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="E13" t="s">
-        <v>675</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>702</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>333</v>
+        <v>703</v>
       </c>
       <c r="C14" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>180</v>
+        <v>670</v>
       </c>
       <c r="E14" t="s">
-        <v>320</v>
+        <v>675</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>680</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C15" t="s">
-        <v>667</v>
+        <v>179</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>668</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>343</v>
+        <v>702</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>342</v>
+        <v>703</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>320</v>
+        <v>702</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>680</v>
+        <v>703</v>
       </c>
       <c r="C16" t="s">
-        <v>179</v>
+        <v>667</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>180</v>
+        <v>668</v>
       </c>
       <c r="E16" t="s">
-        <v>671</v>
+        <v>343</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>254</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>355</v>
+        <v>702</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>354</v>
+        <v>703</v>
       </c>
       <c r="C17" t="s">
-        <v>684</v>
+        <v>179</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>683</v>
+        <v>180</v>
       </c>
       <c r="E17" t="s">
-        <v>320</v>
+        <v>671</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>680</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>355</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>101</v>
+        <v>354</v>
       </c>
       <c r="C18" t="s">
-        <v>179</v>
+        <v>682</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>180</v>
+        <v>681</v>
       </c>
       <c r="E18" t="s">
-        <v>320</v>
+        <v>702</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>680</v>
+        <v>703</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>320</v>
+        <v>102</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>680</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="E19" t="s">
-        <v>366</v>
+        <v>702</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>365</v>
+        <v>703</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>320</v>
+        <v>702</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C20" t="s">
+        <v>202</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E20" t="s">
+        <v>366</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="47" t="s">
+        <v>702</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>703</v>
+      </c>
+      <c r="C21" s="47" t="s">
         <v>680</v>
       </c>
-      <c r="C20" t="s">
-        <v>682</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="D21" s="45" t="s">
+        <v>679</v>
+      </c>
+      <c r="E21" s="47" t="s">
         <v>375</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F21" s="45" t="s">
         <v>380</v>
       </c>
-      <c r="L20" s="46"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>320</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="L21" s="46"/>
+    </row>
+    <row r="22" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="47" t="s">
+        <v>702</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>703</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>680</v>
+      </c>
+      <c r="D22" s="45" t="s">
         <v>679</v>
       </c>
-      <c r="C21" t="s">
-        <v>682</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="E22" s="47" t="s">
         <v>381</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F22" s="45" t="s">
         <v>374</v>
       </c>
-      <c r="L21" s="46"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>320</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="L22" s="46"/>
+    </row>
+    <row r="23" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="47" t="s">
+        <v>702</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>703</v>
+      </c>
+      <c r="C23" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D23" s="45" t="s">
         <v>677</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E23" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F23" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="L22" s="52"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>320</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="L23" s="52"/>
+    </row>
+    <row r="24" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="47" t="s">
+        <v>702</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>703</v>
+      </c>
+      <c r="C24" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="45" t="s">
         <v>677</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" s="47" t="s">
         <v>396</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F24" s="45" t="s">
         <v>395</v>
-      </c>
-      <c r="L23" s="52"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>320</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="L24" s="52"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>320</v>
+        <v>702</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>680</v>
+        <v>703</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>33</v>
+        <v>402</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>32</v>
+        <v>401</v>
       </c>
       <c r="L25" s="52"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>320</v>
+        <v>702</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C26" t="s">
-        <v>181</v>
+        <v>703</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>33</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>40</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="L26" s="52"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>423</v>
+        <v>702</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>422</v>
+        <v>703</v>
       </c>
       <c r="C27" t="s">
-        <v>702</v>
+        <v>181</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>701</v>
+        <v>182</v>
       </c>
       <c r="E27" t="s">
-        <v>320</v>
+        <v>41</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>679</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C28" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="E28" t="s">
-        <v>320</v>
+        <v>702</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>679</v>
+        <v>703</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C29" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="E29" t="s">
-        <v>320</v>
+        <v>702</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>679</v>
+        <v>703</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>637</v>
+        <v>439</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>95</v>
+        <v>438</v>
       </c>
       <c r="C30" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="E30" t="s">
-        <v>320</v>
+        <v>702</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>679</v>
+        <v>703</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>320</v>
+        <v>637</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>679</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="E31" t="s">
-        <v>451</v>
+        <v>702</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="L31" s="46"/>
+        <v>703</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>320</v>
+        <v>702</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>679</v>
+        <v>703</v>
       </c>
       <c r="C32" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="E32" t="s">
-        <v>647</v>
+        <v>451</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>459</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="L32" s="46"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>469</v>
+        <v>702</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>468</v>
+        <v>703</v>
       </c>
       <c r="C33" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="E33" t="s">
-        <v>320</v>
+        <v>647</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>679</v>
+        <v>459</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>469</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C34" t="s">
+        <v>690</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="E34" t="s">
+        <v>702</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>477</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>179</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E34" t="s">
-        <v>320</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
+      <c r="E35" t="s">
+        <v>704</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>482</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="C37" t="s">
-        <v>199</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="E37" t="s">
-        <v>490</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="L37" s="44"/>
-      <c r="M37" s="32"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -9229,95 +9247,96 @@
         <v>481</v>
       </c>
       <c r="C38" t="s">
-        <v>667</v>
+        <v>199</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E38" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="L38" s="44"/>
       <c r="M38" s="32"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>513</v>
+        <v>482</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>512</v>
+        <v>481</v>
       </c>
       <c r="C39" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="E39" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="L39" s="52"/>
+        <v>506</v>
+      </c>
+      <c r="L39" s="44"/>
+      <c r="M39" s="32"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>513</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C40" t="s">
+        <v>673</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="E40" t="s">
         <v>482</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="C40" t="s">
-        <v>690</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="E40" t="s">
-        <v>518</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="L40" s="52"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>671</v>
+        <v>482</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>254</v>
+        <v>481</v>
       </c>
       <c r="C41" t="s">
-        <v>669</v>
+        <v>688</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>668</v>
+        <v>687</v>
       </c>
       <c r="E41" t="s">
-        <v>482</v>
+        <v>518</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>481</v>
+        <v>517</v>
       </c>
       <c r="L41" s="52"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>531</v>
+        <v>671</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>530</v>
+        <v>254</v>
       </c>
       <c r="C42" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="E42" t="s">
         <v>482</v>
@@ -9329,24 +9348,24 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>531</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C43" t="s">
+        <v>682</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="E43" t="s">
         <v>482</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C43" t="s">
-        <v>698</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="E43" t="s">
-        <v>537</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="L43" s="46"/>
+      <c r="L43" s="52"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -9356,127 +9375,128 @@
         <v>481</v>
       </c>
       <c r="C44" t="s">
+        <v>696</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="E44" t="s">
+        <v>537</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="L44" s="46"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>482</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C45" t="s">
         <v>674</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="L44" s="52"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="32" t="s">
+      <c r="L45" s="52"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="32" t="s">
         <v>550</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C46" t="s">
         <v>179</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E46" t="s">
         <v>482</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="L45" s="52"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="L46" s="52"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>482</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="C47" s="32" t="s">
         <v>676</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="L46" s="46"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="44"/>
-      <c r="L47" s="52"/>
+      <c r="L47" s="46"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="48" t="s">
+      <c r="A48" s="44"/>
+      <c r="L48" s="52"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="48" t="s">
         <v>560</v>
       </c>
-      <c r="L48" s="44"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>320</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="L49" s="44"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C50" t="s">
         <v>199</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="E49" s="32" t="s">
+      <c r="E50" s="32" t="s">
         <v>565</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="L49" s="44"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>320</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="L50" s="44"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C51" t="s">
         <v>667</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="E50" s="32" t="s">
+      <c r="E51" s="32" t="s">
         <v>577</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="L50" s="44"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>334</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C51" t="s">
-        <v>179</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E51" t="s">
-        <v>320</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>680</v>
-      </c>
+      <c r="L51" s="44"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>680</v>
+        <v>333</v>
       </c>
       <c r="C52" t="s">
         <v>179</v>
@@ -9484,373 +9504,392 @@
       <c r="D52" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E53" t="s">
         <v>671</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>254</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>355</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C53" t="s">
-        <v>684</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="E53" t="s">
-        <v>320</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>355</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C54" t="s">
+        <v>682</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B55" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" s="47" t="s">
         <v>179</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D55" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="E54" t="s">
-        <v>320</v>
-      </c>
-      <c r="F54" s="1" t="s">
+      <c r="E55" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="F55" s="45" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B56" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="C56" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="D56" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="E56" s="47" t="s">
+        <v>366</v>
+      </c>
+      <c r="F56" s="45" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B57" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="C57" s="47" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>320</v>
-      </c>
-      <c r="B55" s="1" t="s">
+      <c r="D57" s="45" t="s">
+        <v>679</v>
+      </c>
+      <c r="E57" s="47" t="s">
+        <v>375</v>
+      </c>
+      <c r="F57" s="45" t="s">
+        <v>380</v>
+      </c>
+      <c r="L57" s="46"/>
+    </row>
+    <row r="58" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B58" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="C58" s="47" t="s">
         <v>680</v>
       </c>
-      <c r="C55" t="s">
-        <v>202</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E55" t="s">
-        <v>366</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>320</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C56" t="s">
-        <v>682</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="E56" t="s">
-        <v>375</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="L56" s="46"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>320</v>
-      </c>
-      <c r="B57" s="1" t="s">
+      <c r="D58" s="45" t="s">
         <v>679</v>
       </c>
-      <c r="C57" t="s">
-        <v>682</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="E58" s="47" t="s">
         <v>381</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F58" s="45" t="s">
         <v>374</v>
       </c>
-      <c r="L57" s="46"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>320</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="L58" s="46"/>
+    </row>
+    <row r="59" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B59" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="C59" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D59" s="45" t="s">
         <v>677</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E59" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F59" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="L58" s="52"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>320</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="L59" s="52"/>
+    </row>
+    <row r="60" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B60" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="C60" s="47" t="s">
         <v>678</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D60" s="45" t="s">
         <v>677</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E60" s="47" t="s">
         <v>396</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F60" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="L59" s="52"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>320</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C60" s="32" t="s">
+      <c r="L60" s="52"/>
+    </row>
+    <row r="61" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B61" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="C61" s="44" t="s">
         <v>402</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D61" s="45" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>320</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C61" s="32" t="s">
+      <c r="F61" s="45"/>
+    </row>
+    <row r="62" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B62" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="C62" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D62" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="L61" s="46"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>320</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="F62" s="45"/>
+      <c r="L62" s="46"/>
+    </row>
+    <row r="63" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B63" s="45" t="s">
+        <v>701</v>
+      </c>
+      <c r="C63" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D63" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E63" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F63" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="L62" s="46"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="L63" s="46"/>
+    </row>
+    <row r="64" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="47" t="s">
         <v>423</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B64" s="45" t="s">
         <v>422</v>
       </c>
-      <c r="C63" t="s">
-        <v>702</v>
-      </c>
-      <c r="D63" s="1" t="s">
+      <c r="C64" s="47" t="s">
+        <v>700</v>
+      </c>
+      <c r="D64" s="45" t="s">
+        <v>699</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="F64" s="45" t="s">
         <v>701</v>
       </c>
-      <c r="E63" t="s">
-        <v>320</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    </row>
+    <row r="65" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="47" t="s">
         <v>431</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="45" t="s">
         <v>430</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C65" s="47" t="s">
+        <v>690</v>
+      </c>
+      <c r="D65" s="45" t="s">
+        <v>689</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="F65" s="45" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="47" t="s">
+        <v>633</v>
+      </c>
+      <c r="B66" s="45" t="s">
+        <v>632</v>
+      </c>
+      <c r="C66" s="47" t="s">
         <v>692</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D66" s="45" t="s">
         <v>691</v>
       </c>
-      <c r="E64" t="s">
-        <v>320</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>633</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="E66" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="F66" s="45" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="47" t="s">
+        <v>637</v>
+      </c>
+      <c r="B67" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="C67" s="47" t="s">
         <v>694</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D67" s="45" t="s">
         <v>693</v>
       </c>
-      <c r="E65" t="s">
-        <v>320</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>637</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="E67" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="F67" s="45" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C68" t="s">
         <v>696</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="E66" t="s">
-        <v>320</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>320</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="E68" t="s">
+        <v>451</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="L68" s="46"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C69" t="s">
         <v>698</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="E67" t="s">
-        <v>451</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="L67" s="46"/>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>320</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C68" t="s">
-        <v>700</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="E69" t="s">
         <v>647</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="70" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="47" t="s">
         <v>469</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B70" s="45" t="s">
         <v>468</v>
       </c>
-      <c r="C69" t="s">
-        <v>692</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="E69" t="s">
-        <v>320</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="C70" s="47" t="s">
+        <v>690</v>
+      </c>
+      <c r="D70" s="45" t="s">
+        <v>689</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="F70" s="45" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="47" t="s">
         <v>477</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B71" s="45" t="s">
         <v>476</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C71" s="47" t="s">
         <v>179</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D71" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="E70" t="s">
-        <v>320</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L71" s="46"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L73" s="46"/>
+      <c r="E71" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="F71" s="45" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L72" s="46"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L74" s="46"/>
@@ -9859,19 +9898,19 @@
       <c r="L75" s="46"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L76" s="44"/>
+      <c r="L76" s="46"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L77" s="44"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L78" s="46"/>
+      <c r="L78" s="44"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L79" s="52"/>
+      <c r="L79" s="46"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L80" s="44"/>
+      <c r="L80" s="52"/>
     </row>
     <row r="81" spans="12:12" x14ac:dyDescent="0.3">
       <c r="L81" s="44"/>
@@ -9883,7 +9922,7 @@
       <c r="L83" s="44"/>
     </row>
     <row r="84" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L84" s="46"/>
+      <c r="L84" s="44"/>
     </row>
     <row r="85" spans="12:12" x14ac:dyDescent="0.3">
       <c r="L85" s="46"/>
@@ -9937,7 +9976,7 @@
       <c r="L101" s="46"/>
     </row>
     <row r="102" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L102" s="66"/>
+      <c r="L102" s="46"/>
     </row>
     <row r="103" spans="12:12" x14ac:dyDescent="0.3">
       <c r="L103" s="66"/>
@@ -9946,16 +9985,16 @@
       <c r="L104" s="66"/>
     </row>
     <row r="105" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L105" s="46"/>
+      <c r="L105" s="66"/>
     </row>
     <row r="106" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L106" s="52"/>
+      <c r="L106" s="46"/>
     </row>
     <row r="107" spans="12:12" x14ac:dyDescent="0.3">
       <c r="L107" s="52"/>
     </row>
     <row r="108" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L108" s="46"/>
+      <c r="L108" s="52"/>
     </row>
     <row r="109" spans="12:12" x14ac:dyDescent="0.3">
       <c r="L109" s="46"/>
@@ -9973,76 +10012,51 @@
       <c r="L113" s="46"/>
     </row>
     <row r="114" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L114" s="44"/>
+      <c r="L114" s="46"/>
     </row>
     <row r="115" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L115" s="76"/>
+      <c r="L115" s="44"/>
     </row>
     <row r="116" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L116" s="44"/>
+      <c r="L116" s="76"/>
     </row>
     <row r="117" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L117" s="46"/>
+      <c r="L117" s="44"/>
     </row>
     <row r="118" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L118" s="52"/>
+      <c r="L118" s="46"/>
     </row>
     <row r="119" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L119" s="46"/>
+      <c r="L119" s="52"/>
+    </row>
+    <row r="120" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L120" s="46"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1"/>
     <hyperlink ref="B5" r:id="rId2"/>
-    <hyperlink ref="B41" r:id="rId3"/>
-    <hyperlink ref="C44" r:id="rId4" display="https://www.google.com/search?q=http://purl.obolibrary.org/obo/RO_0002351"/>
-    <hyperlink ref="D44" r:id="rId5" display="https://www.google.com/search?q=http://purl.obolibrary.org/obo/RO_0002351"/>
-    <hyperlink ref="B45" r:id="rId6"/>
-    <hyperlink ref="D46" r:id="rId7"/>
-    <hyperlink ref="F49" r:id="rId8"/>
-    <hyperlink ref="B49" r:id="rId9"/>
-    <hyperlink ref="B13" r:id="rId10"/>
-    <hyperlink ref="B6" r:id="rId11"/>
-    <hyperlink ref="F7" r:id="rId12"/>
-    <hyperlink ref="F8" r:id="rId13"/>
-    <hyperlink ref="F9" r:id="rId14"/>
-    <hyperlink ref="B10" r:id="rId15"/>
-    <hyperlink ref="B59:B60" r:id="rId16" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="B55:B56" r:id="rId17" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="B23" r:id="rId18" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="B20" r:id="rId19" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="B26" r:id="rId20" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="B15" r:id="rId21"/>
-    <hyperlink ref="F16" r:id="rId22"/>
-    <hyperlink ref="B68" r:id="rId23" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F68" r:id="rId24"/>
-    <hyperlink ref="F52" r:id="rId25"/>
-    <hyperlink ref="B62" r:id="rId26" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="D24" r:id="rId27"/>
-    <hyperlink ref="D25" r:id="rId28"/>
-    <hyperlink ref="D60" r:id="rId29"/>
-    <hyperlink ref="D61" r:id="rId30"/>
-    <hyperlink ref="B60:B61" r:id="rId31" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="B24:B25" r:id="rId32" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F27" r:id="rId33" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F28" r:id="rId34" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F29" r:id="rId35" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F30" r:id="rId36" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F32" r:id="rId37"/>
-    <hyperlink ref="F33" r:id="rId38" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F34" r:id="rId39" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="B50" r:id="rId40"/>
-    <hyperlink ref="F63" r:id="rId41" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F64" r:id="rId42" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F65" r:id="rId43" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F66" r:id="rId44" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F69" r:id="rId45" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="F70" r:id="rId46" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="B32" r:id="rId47" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="B67" r:id="rId48" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
-    <hyperlink ref="B31" r:id="rId49" display="http://purl.obolibrary.org/obo/OBIB_0000670"/>
+    <hyperlink ref="B42" r:id="rId3"/>
+    <hyperlink ref="C45" r:id="rId4" display="https://www.google.com/search?q=http://purl.obolibrary.org/obo/RO_0002351"/>
+    <hyperlink ref="D45" r:id="rId5" display="https://www.google.com/search?q=http://purl.obolibrary.org/obo/RO_0002351"/>
+    <hyperlink ref="B46" r:id="rId6"/>
+    <hyperlink ref="D47" r:id="rId7"/>
+    <hyperlink ref="F50" r:id="rId8"/>
+    <hyperlink ref="B6" r:id="rId9"/>
+    <hyperlink ref="F7" r:id="rId10"/>
+    <hyperlink ref="F8" r:id="rId11"/>
+    <hyperlink ref="F9" r:id="rId12"/>
+    <hyperlink ref="B10" r:id="rId13"/>
+    <hyperlink ref="F17" r:id="rId14"/>
+    <hyperlink ref="F69" r:id="rId15"/>
+    <hyperlink ref="F53" r:id="rId16"/>
+    <hyperlink ref="D25" r:id="rId17"/>
+    <hyperlink ref="D26" r:id="rId18"/>
+    <hyperlink ref="D61" r:id="rId19"/>
+    <hyperlink ref="D62" r:id="rId20"/>
+    <hyperlink ref="F33" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId50"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>
--- a/ΟΒΙΒv2.2/Biobank, Collection, Network, Research Resource(v2.2).xlsx
+++ b/ΟΒΙΒv2.2/Biobank, Collection, Network, Research Resource(v2.2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="sample,sample donor,event(v2.1)" sheetId="1" r:id="rId1"/>

--- a/ΟΒΙΒv2.2/Biobank, Collection, Network, Research Resource(v2.2).xlsx
+++ b/ΟΒΙΒv2.2/Biobank, Collection, Network, Research Resource(v2.2).xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="789">
   <si>
     <t>Entity</t>
   </si>
@@ -376,31 +376,6 @@
     <t>use and access condition</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Allowed values</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:Commercial use, Collaboration, Specific research use, Genetic data use, Outside EU access, Xenograft, Other animal work, Other.</t>
-    </r>
-  </si>
-  <si>
     <t>MIABIS-SAMPLE-12</t>
   </si>
   <si>
@@ -414,31 +389,6 @@
   </si>
   <si>
     <t>sample source</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Allowed values:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Human, Animal, Environment.</t>
-    </r>
   </si>
   <si>
     <t>Sample Donor</t>
@@ -548,31 +498,6 @@
     <t>"donor's biological sex" class already existed in the ontology. Now it is connected with "specimen donor".</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Allowed values</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Biological sex of the sample donor. Can be one of the following values: Male, Female, Unknown, Undifferentiated, Not applicable</t>
-    </r>
-  </si>
-  <si>
     <t>MIABIS-SAMPLEDONOR-04</t>
   </si>
   <si>
@@ -2428,6 +2353,330 @@
   </si>
   <si>
     <t>member of</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002076</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002074</t>
+  </si>
+  <si>
+    <t>human</t>
+  </si>
+  <si>
+    <t>animal</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002077</t>
+  </si>
+  <si>
+    <t>environment</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>classes:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Human, Animal, Environment.</t>
+    </r>
+  </si>
+  <si>
+    <t>Commercial use</t>
+  </si>
+  <si>
+    <t>Collaboration</t>
+  </si>
+  <si>
+    <t>Genetic data use</t>
+  </si>
+  <si>
+    <t>Outside EU access</t>
+  </si>
+  <si>
+    <t>Xenograft</t>
+  </si>
+  <si>
+    <t>Specific research use</t>
+  </si>
+  <si>
+    <t>Other animal work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type of </t>
+  </si>
+  <si>
+    <t xml:space="preserve">use and access conditions </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>New related Individuals</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:Commercial use, Collaboration, Specific research use, Genetic data use, Outside EU access, Xenograft, Other animal work, Other.</t>
+    </r>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002078</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002079</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002083</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002084</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002082</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002080</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002081</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OMRSE_00000210</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OMRSE_00000211</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OMRSE_00000212</t>
+  </si>
+  <si>
+    <t>female gender identity information content entity</t>
+  </si>
+  <si>
+    <t>male gender identity information content entity</t>
+  </si>
+  <si>
+    <t>non-binary identity information content entity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Already existed classes, connected to donor biological sex</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Allowed Values: Male, Female, Unknown, Undifferentiated, Not applicable</t>
+    </r>
+  </si>
+  <si>
+    <t>has subclass</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002087</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002086</t>
+  </si>
+  <si>
+    <t>biosafety abilities</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002085</t>
+  </si>
+  <si>
+    <t>sample storage</t>
+  </si>
+  <si>
+    <t>data storage</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Recontact with donors</t>
+  </si>
+  <si>
+    <t>Facilitating clinical trials</t>
+  </si>
+  <si>
+    <t>Setting up prospective collections</t>
+  </si>
+  <si>
+    <t>Access to omics data</t>
+  </si>
+  <si>
+    <t>Access to laboratory analysis data</t>
+  </si>
+  <si>
+    <t>Access to donors'clinical data</t>
+  </si>
+  <si>
+    <t>Access to pathology archive</t>
+  </si>
+  <si>
+    <t>Access to radiology archive</t>
+  </si>
+  <si>
+    <t>Access to national medical registries</t>
+  </si>
+  <si>
+    <t>Biochemical analyses</t>
+  </si>
+  <si>
+    <t>Genomics</t>
+  </si>
+  <si>
+    <t>Nucleic acid extraction</t>
+  </si>
+  <si>
+    <t>Proteomics</t>
+  </si>
+  <si>
+    <t>Metabolomics</t>
+  </si>
+  <si>
+    <t>Cell-lines processing</t>
+  </si>
+  <si>
+    <t>Sample processing</t>
+  </si>
+  <si>
+    <t>Sample shipping</t>
+  </si>
+  <si>
+    <t>Sample quality control services</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002095</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002089</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002092</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002090</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002091</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002088</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002096</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002094</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002093</t>
+  </si>
+  <si>
+    <t>Virological analysis</t>
+  </si>
+  <si>
+    <t>Histological analysis</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002100</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002098</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002101</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002102</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002103</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002104</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002105</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002106</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002107</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002108</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002109</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002110</t>
+  </si>
+  <si>
+    <t>ISO 20387</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002111</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002097</t>
+  </si>
+  <si>
+    <t>ISO 9001</t>
   </si>
 </sst>
 </file>
@@ -2771,7 +3020,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2799,6 +3048,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2872,7 +3127,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3013,6 +3268,7 @@
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4070,7 +4326,7 @@
         <v>26</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>97</v>
+        <v>720</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>15</v>
@@ -4098,33 +4354,33 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>53</v>
       </c>
       <c r="D15" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" s="25" t="s">
         <v>99</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>100</v>
       </c>
       <c r="F15" s="25" t="s">
         <v>56</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="I15" s="25" t="s">
-        <v>102</v>
-      </c>
       <c r="J15" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K15" s="25"/>
       <c r="L15" s="13" t="s">
-        <v>103</v>
+        <v>710</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>15</v>
@@ -4179,7 +4435,7 @@
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B17" s="28" t="s">
         <v>15</v>
@@ -4189,19 +4445,19 @@
       <c r="E17" s="29"/>
       <c r="F17" s="28"/>
       <c r="G17" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H17" s="16" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>106</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17" s="25" t="s">
-        <v>108</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>15</v>
@@ -4224,40 +4480,40 @@
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B18" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="25" t="s">
+      <c r="F18" s="25" t="s">
         <v>110</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>112</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="J18" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="K18" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="I18" s="25" t="s">
+      <c r="L18" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="J18" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N18" s="3"/>
       <c r="P18" s="3"/>
@@ -4277,40 +4533,40 @@
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B19" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="25" t="s">
+      <c r="F19" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="G19" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="K19" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="J19" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K19" s="25" t="s">
-        <v>124</v>
-      </c>
       <c r="L19" s="13" t="s">
-        <v>125</v>
+        <v>734</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>15</v>
@@ -4335,38 +4591,38 @@
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B20" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="25" t="s">
         <v>126</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>129</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J20" s="25"/>
       <c r="K20" s="27" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>15</v>
@@ -4391,43 +4647,43 @@
     </row>
     <row r="21" spans="1:30" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D21" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="E21" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>137</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="67" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J21" s="25" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K21" s="70" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>15</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>15</v>
@@ -4477,7 +4733,7 @@
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -4486,16 +4742,16 @@
       <c r="F23" s="5"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J23" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>15</v>
@@ -4518,38 +4774,38 @@
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13"/>
       <c r="H24" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J24" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="L24" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N24" s="3"/>
       <c r="P24" s="3"/>
@@ -4569,41 +4825,41 @@
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G25" s="13"/>
       <c r="H25" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J25" s="25" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="L25" s="13" t="s">
         <v>15</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="N25" s="3"/>
       <c r="P25" s="3"/>
@@ -4623,41 +4879,41 @@
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G26" s="13"/>
       <c r="H26" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J26" s="25" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="L26" s="13" t="s">
         <v>15</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="N26" s="3"/>
       <c r="P26" s="3"/>
@@ -4677,41 +4933,41 @@
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I27" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="L27" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="J27" s="25" t="s">
+      <c r="M27" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>15</v>
@@ -4822,35 +5078,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.6640625" customWidth="1"/>
+    <col min="4" max="4" width="47.77734375" customWidth="1"/>
     <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -4861,10 +5117,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
@@ -4881,10 +5137,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>41</v>
@@ -4901,10 +5157,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>50</v>
@@ -4921,10 +5177,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>58</v>
@@ -4941,16 +5197,16 @@
         <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -4958,19 +5214,19 @@
         <v>58</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -4978,19 +5234,19 @@
         <v>58</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -4998,19 +5254,19 @@
         <v>58</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>79</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -5021,10 +5277,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>86</v>
@@ -5041,10 +5297,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>96</v>
@@ -5061,16 +5317,16 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -5080,99 +5336,99 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" t="s">
+        <v>203</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="E17" t="s">
-        <v>206</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
@@ -5188,82 +5444,82 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E20" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C22" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C23" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -5278,13 +5534,58 @@
       <c r="D26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>735</v>
+      </c>
       <c r="D27" s="11"/>
+      <c r="E27" t="s">
+        <v>706</v>
+      </c>
+      <c r="F27" t="s">
+        <v>704</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>735</v>
+      </c>
       <c r="D28" s="11"/>
+      <c r="E28" t="s">
+        <v>707</v>
+      </c>
+      <c r="F28" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>735</v>
+      </c>
       <c r="D29" s="11"/>
+      <c r="E29" t="s">
+        <v>709</v>
+      </c>
+      <c r="F29" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D30" s="11"/>
@@ -5293,10 +5594,201 @@
       <c r="D31" s="11"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D32" s="11"/>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>719</v>
+      </c>
+      <c r="B32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" t="s">
+        <v>718</v>
+      </c>
+      <c r="E32" t="s">
+        <v>711</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>719</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" t="s">
+        <v>718</v>
+      </c>
       <c r="D33" s="11"/>
+      <c r="E33" t="s">
+        <v>712</v>
+      </c>
+      <c r="F33" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>719</v>
+      </c>
+      <c r="B34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" t="s">
+        <v>718</v>
+      </c>
+      <c r="E34" t="s">
+        <v>716</v>
+      </c>
+      <c r="F34" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>719</v>
+      </c>
+      <c r="B35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" t="s">
+        <v>718</v>
+      </c>
+      <c r="E35" t="s">
+        <v>713</v>
+      </c>
+      <c r="F35" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>719</v>
+      </c>
+      <c r="B36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" t="s">
+        <v>718</v>
+      </c>
+      <c r="E36" t="s">
+        <v>714</v>
+      </c>
+      <c r="F36" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>719</v>
+      </c>
+      <c r="B37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" t="s">
+        <v>718</v>
+      </c>
+      <c r="E37" t="s">
+        <v>715</v>
+      </c>
+      <c r="F37" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>719</v>
+      </c>
+      <c r="B38" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" t="s">
+        <v>718</v>
+      </c>
+      <c r="E38" t="s">
+        <v>717</v>
+      </c>
+      <c r="F38" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>719</v>
+      </c>
+      <c r="B39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" t="s">
+        <v>718</v>
+      </c>
+      <c r="E39" t="s">
+        <v>785</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>363</v>
+      </c>
+      <c r="B41" t="s">
+        <v>362</v>
+      </c>
+      <c r="C41" t="s">
+        <v>199</v>
+      </c>
+      <c r="D41" t="s">
+        <v>200</v>
+      </c>
+      <c r="E41" t="s">
+        <v>731</v>
+      </c>
+      <c r="F41" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>363</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C42" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E42" t="s">
+        <v>732</v>
+      </c>
+      <c r="F42" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>363</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C43" t="s">
+        <v>199</v>
+      </c>
+      <c r="D43" t="s">
+        <v>200</v>
+      </c>
+      <c r="E43" t="s">
+        <v>733</v>
+      </c>
+      <c r="F43" t="s">
+        <v>730</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5338,9 +5830,13 @@
     <hyperlink ref="B23" r:id="rId36"/>
     <hyperlink ref="D14" r:id="rId37"/>
     <hyperlink ref="F17" r:id="rId38"/>
+    <hyperlink ref="B28" r:id="rId39"/>
+    <hyperlink ref="B42" r:id="rId40"/>
+    <hyperlink ref="B43" r:id="rId41"/>
+    <hyperlink ref="D42" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId39"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId43"/>
 </worksheet>
 </file>
 
@@ -5372,7 +5868,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>3</v>
@@ -5423,7 +5919,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
@@ -5435,460 +5931,460 @@
       <c r="I2" s="39"/>
       <c r="J2" s="39"/>
       <c r="K2" s="38" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="D3" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E3" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="F3" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="G3" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="H3" s="32"/>
       <c r="I3" s="32" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J3" s="38" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="L3" s="32"/>
       <c r="M3" s="32" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B4" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>230</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>233</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>64</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H4" s="32"/>
       <c r="I4" s="32" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L4" s="32"/>
       <c r="M4" s="32"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B5" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>238</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>239</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>241</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>64</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H5" s="32"/>
       <c r="I5" s="32" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L5" s="32"/>
       <c r="M5" s="32"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B6" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" s="32" t="s">
         <v>242</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>245</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>64</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="32" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="L6" s="32"/>
       <c r="M6" s="32"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B7" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="E7" s="32" t="s">
         <v>250</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>252</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>253</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>64</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H7" s="32"/>
       <c r="I7" s="32" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B8" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="E8" s="32" t="s">
         <v>258</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>261</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>64</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H8" s="32"/>
       <c r="I8" s="32" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="L8" s="32"/>
       <c r="M8" s="32" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B9" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="E9" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="F9" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="G9" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="H9" s="32"/>
       <c r="I9" s="32" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M9" s="32"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B10" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="E10" s="32" t="s">
         <v>276</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>279</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>64</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H10" s="32"/>
       <c r="I10" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="L10" s="32"/>
       <c r="M10" s="32" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C11" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D11" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="G11" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="H11" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="I11" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="J11" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="K11" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="L11" s="32" t="s">
         <v>290</v>
-      </c>
-      <c r="I11" s="32" t="s">
-        <v>291</v>
-      </c>
-      <c r="J11" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="K11" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="L11" s="32" t="s">
-        <v>293</v>
       </c>
       <c r="M11" s="32"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C12" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="I12" s="32" t="s">
         <v>296</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="J12" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="K12" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="L12" s="32" t="s">
         <v>298</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="J12" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="K12" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="L12" s="32" t="s">
-        <v>301</v>
       </c>
       <c r="M12" s="32"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C13" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D13" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="I13" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="J13" s="32" t="s">
         <v>305</v>
       </c>
-      <c r="G13" s="38" t="s">
+      <c r="K13" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="L13" s="44" t="s">
         <v>306</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>308</v>
-      </c>
-      <c r="K13" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="L13" s="32" t="s">
-        <v>309</v>
       </c>
       <c r="M13" s="32"/>
     </row>
     <row r="14" spans="1:30" s="32" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C14" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D14" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="I14" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="J14" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="L14" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="G14" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="H14" s="1" t="s">
+      <c r="M14" s="32" t="s">
         <v>314</v>
-      </c>
-      <c r="I14" s="32" t="s">
-        <v>315</v>
-      </c>
-      <c r="J14" s="32" t="s">
-        <v>312</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="L14" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="M14" s="32" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B15" s="33"/>
       <c r="C15" s="33"/>
@@ -5896,524 +6392,524 @@
       <c r="E15" s="33"/>
       <c r="F15" s="33"/>
       <c r="G15" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="32" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J15" s="32" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K15" s="25" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L15" s="32"/>
       <c r="M15" s="32"/>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B16" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>324</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="H16" s="32"/>
       <c r="I16" s="32" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="L16" s="32"/>
       <c r="M16" s="32" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F17" s="32" t="s">
         <v>64</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H17" s="32"/>
       <c r="I17" s="32" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="L17" s="32"/>
       <c r="M17" s="32"/>
     </row>
     <row r="18" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F18" s="32" t="s">
         <v>64</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H18" s="32"/>
       <c r="I18" s="32" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J18" s="64" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="L18" s="32"/>
       <c r="M18" s="32"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B19" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>337</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C19" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="E19" s="32" t="s">
+      <c r="I19" s="32" t="s">
         <v>340</v>
       </c>
-      <c r="F19" s="32" t="s">
+      <c r="J19" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="G19" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="H19" s="1" t="s">
+      <c r="K19" s="25" t="s">
         <v>342</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="J19" s="32" t="s">
-        <v>344</v>
-      </c>
-      <c r="K19" s="25" t="s">
-        <v>345</v>
       </c>
       <c r="L19" s="32"/>
       <c r="M19" s="32"/>
     </row>
     <row r="20" spans="1:13" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="44" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B20" s="44" t="s">
+        <v>343</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>344</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>345</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="I20" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="J20" s="46" t="s">
         <v>346</v>
       </c>
-      <c r="C20" s="44" t="s">
-        <v>268</v>
-      </c>
-      <c r="D20" s="44" t="s">
-        <v>269</v>
-      </c>
-      <c r="E20" s="44" t="s">
+      <c r="K20" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="L20" s="44" t="s">
         <v>348</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>289</v>
-      </c>
-      <c r="H20" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="I20" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="J20" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="K20" s="26" t="s">
-        <v>350</v>
-      </c>
-      <c r="L20" s="44" t="s">
-        <v>351</v>
       </c>
       <c r="M20" s="44"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F21" s="32" t="s">
         <v>64</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H21" s="32"/>
       <c r="I21" s="32" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="L21" s="32"/>
       <c r="M21" s="32" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C22" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D22" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="F22" s="32" t="s">
+        <v>356</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="32" t="s">
-        <v>359</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="32" t="s">
         <v>101</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>102</v>
       </c>
       <c r="J22" s="38"/>
       <c r="K22" s="25" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="L22" s="32" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="M22" s="32"/>
     </row>
     <row r="23" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B23" s="32" t="s">
+        <v>358</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>359</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="F23" s="32" t="s">
         <v>361</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="G23" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>363</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>364</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="H23" s="32"/>
       <c r="I23" s="32" t="s">
+        <v>363</v>
+      </c>
+      <c r="J23" s="41" t="s">
+        <v>364</v>
+      </c>
+      <c r="K23" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="L23" s="32" t="s">
         <v>366</v>
-      </c>
-      <c r="J23" s="41" t="s">
-        <v>367</v>
-      </c>
-      <c r="K23" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="L23" s="32" t="s">
-        <v>369</v>
       </c>
       <c r="M23" s="32"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B24" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="E24" s="32" t="s">
         <v>370</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>371</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>372</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>373</v>
       </c>
       <c r="F24" s="32" t="s">
         <v>64</v>
       </c>
       <c r="G24" s="32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I24" s="32" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="J24" s="38" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="K24" s="25" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="L24" s="32"/>
       <c r="M24" s="32"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B25" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>375</v>
+      </c>
+      <c r="E25" s="32" t="s">
         <v>376</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>377</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>378</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>379</v>
       </c>
       <c r="F25" s="32" t="s">
         <v>64</v>
       </c>
       <c r="G25" s="32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I25" s="32" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="K25" s="25" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="L25" s="32"/>
       <c r="M25" s="32"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B26" s="32" t="s">
+        <v>379</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>380</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>381</v>
+      </c>
+      <c r="E26" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="F26" s="32" t="s">
         <v>383</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="G26" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="I26" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="F26" s="32" t="s">
+      <c r="J26" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="K26" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="L26" s="32" t="s">
         <v>386</v>
-      </c>
-      <c r="G26" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="I26" s="32" t="s">
-        <v>388</v>
-      </c>
-      <c r="J26" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="K26" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="L26" s="32" t="s">
-        <v>389</v>
       </c>
       <c r="M26" s="32"/>
     </row>
     <row r="27" spans="1:13" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="44" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B27" s="44" t="s">
+        <v>387</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>388</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>389</v>
+      </c>
+      <c r="E27" s="44" t="s">
         <v>390</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="F27" s="44" t="s">
         <v>391</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="G27" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="H27" s="45" t="s">
         <v>392</v>
       </c>
-      <c r="E27" s="44" t="s">
+      <c r="I27" s="44" t="s">
         <v>393</v>
       </c>
-      <c r="F27" s="44" t="s">
-        <v>394</v>
-      </c>
-      <c r="G27" s="44" t="s">
-        <v>289</v>
-      </c>
-      <c r="H27" s="45" t="s">
-        <v>395</v>
-      </c>
-      <c r="I27" s="44" t="s">
-        <v>396</v>
-      </c>
       <c r="J27" s="44" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="K27" s="26" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="L27" s="44" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M27" s="44"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B28" s="32" t="s">
+        <v>394</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>396</v>
+      </c>
+      <c r="F28" s="32" t="s">
         <v>397</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="G28" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D28" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" s="32" t="s">
+      <c r="I28" s="32" t="s">
         <v>399</v>
       </c>
-      <c r="F28" s="32" t="s">
+      <c r="K28" s="43" t="s">
         <v>400</v>
       </c>
-      <c r="G28" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H28" s="1" t="s">
+      <c r="L28" s="78" t="s">
         <v>401</v>
-      </c>
-      <c r="I28" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="K28" s="43" t="s">
-        <v>403</v>
-      </c>
-      <c r="L28" s="32" t="s">
-        <v>404</v>
       </c>
       <c r="M28" s="32"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D29" s="32" t="s">
         <v>29</v>
       </c>
       <c r="E29" s="32" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G29" s="32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>32</v>
@@ -6423,31 +6919,31 @@
       </c>
       <c r="J29" s="32"/>
       <c r="K29" s="25" t="s">
-        <v>409</v>
-      </c>
-      <c r="L29" s="32" t="s">
-        <v>410</v>
+        <v>406</v>
+      </c>
+      <c r="L29" s="78" t="s">
+        <v>407</v>
       </c>
       <c r="M29" s="32"/>
     </row>
     <row r="30" spans="1:13" s="47" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="44" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B30" s="44" t="s">
+        <v>408</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>409</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>410</v>
+      </c>
+      <c r="E30" s="44" t="s">
         <v>411</v>
       </c>
-      <c r="C30" s="44" t="s">
+      <c r="F30" s="44" t="s">
         <v>412</v>
-      </c>
-      <c r="D30" s="44" t="s">
-        <v>413</v>
-      </c>
-      <c r="E30" s="44" t="s">
-        <v>414</v>
-      </c>
-      <c r="F30" s="44" t="s">
-        <v>415</v>
       </c>
       <c r="G30" s="45" t="s">
         <v>40</v>
@@ -6460,134 +6956,134 @@
         <v>42</v>
       </c>
       <c r="K30" s="46" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="L30" s="44" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="M30" s="44"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B31" s="32" t="s">
+        <v>414</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>415</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="E31" s="32" t="s">
         <v>417</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="F31" s="32" t="s">
         <v>418</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="G31" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="E31" s="32" t="s">
-        <v>420</v>
-      </c>
-      <c r="F31" s="32" t="s">
-        <v>421</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="H31" s="32"/>
       <c r="I31" s="32" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="J31" s="61" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="L31" s="32" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="M31" s="32"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C32" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D32" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="E32" s="32" t="s">
+        <v>425</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>426</v>
+      </c>
+      <c r="G32" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E32" s="32" t="s">
+      <c r="I32" s="32" t="s">
         <v>428</v>
       </c>
-      <c r="F32" s="32" t="s">
+      <c r="J32" s="61" t="s">
+        <v>425</v>
+      </c>
+      <c r="K32" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="L32" s="78" t="s">
         <v>429</v>
-      </c>
-      <c r="G32" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="I32" s="32" t="s">
-        <v>431</v>
-      </c>
-      <c r="J32" s="61" t="s">
-        <v>428</v>
-      </c>
-      <c r="K32" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="L32" s="32" t="s">
-        <v>432</v>
       </c>
       <c r="M32" s="32"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B33" s="32" t="s">
+        <v>430</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>431</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="E33" s="32" t="s">
         <v>433</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="F33" s="32" t="s">
         <v>434</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="G33" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="E33" s="32" t="s">
+      <c r="I33" s="32" t="s">
         <v>436</v>
       </c>
-      <c r="F33" s="32" t="s">
+      <c r="J33" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="K33" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="L33" s="78" t="s">
         <v>437</v>
-      </c>
-      <c r="G33" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="I33" s="32" t="s">
-        <v>439</v>
-      </c>
-      <c r="J33" s="32" t="s">
-        <v>436</v>
-      </c>
-      <c r="K33" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="L33" s="32" t="s">
-        <v>440</v>
       </c>
       <c r="M33" s="32"/>
     </row>
     <row r="34" spans="1:13" s="47" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="44" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C34" s="44" t="s">
         <v>53</v>
@@ -6596,184 +7092,184 @@
         <v>92</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F34" s="44" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G34" s="44" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H34" s="45" t="s">
         <v>95</v>
       </c>
       <c r="I34" s="44" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J34" s="62" t="s">
         <v>93</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="L34" s="44" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="M34" s="44"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C35" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D35" s="32" t="s">
+        <v>444</v>
+      </c>
+      <c r="E35" s="32" t="s">
+        <v>445</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>446</v>
+      </c>
+      <c r="G35" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="E35" s="32" t="s">
+      <c r="I35" s="32" t="s">
         <v>448</v>
       </c>
-      <c r="F35" s="32" t="s">
+      <c r="J35" s="32" t="s">
         <v>449</v>
       </c>
-      <c r="G35" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H35" s="1" t="s">
+      <c r="K35" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="L35" s="78" t="s">
         <v>450</v>
-      </c>
-      <c r="I35" s="32" t="s">
-        <v>451</v>
-      </c>
-      <c r="J35" s="32" t="s">
-        <v>452</v>
-      </c>
-      <c r="K35" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="L35" s="32" t="s">
-        <v>453</v>
       </c>
       <c r="M35" s="32"/>
     </row>
     <row r="36" spans="1:13" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B36" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>452</v>
+      </c>
+      <c r="D36" s="32" t="s">
+        <v>453</v>
+      </c>
+      <c r="E36" s="32" t="s">
         <v>454</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="F36" s="32" t="s">
         <v>455</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="G36" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="E36" s="32" t="s">
-        <v>457</v>
-      </c>
-      <c r="F36" s="32" t="s">
-        <v>458</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="H36" s="32"/>
       <c r="I36" s="32" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="J36" s="55" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="L36" s="32"/>
       <c r="M36" s="32"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B37" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>461</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E37" s="32" t="s">
         <v>463</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="F37" s="32" t="s">
         <v>464</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="G37" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="E37" s="32" t="s">
-        <v>466</v>
-      </c>
-      <c r="F37" s="32" t="s">
-        <v>467</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="H37" s="32"/>
       <c r="I37" s="32" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>462</v>
-      </c>
-      <c r="L37" s="32" t="s">
-        <v>471</v>
+        <v>459</v>
+      </c>
+      <c r="L37" s="78" t="s">
+        <v>468</v>
       </c>
       <c r="M37" s="32"/>
     </row>
     <row r="38" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C38" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D38" s="32" t="s">
+        <v>470</v>
+      </c>
+      <c r="E38" s="32" t="s">
+        <v>471</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>472</v>
+      </c>
+      <c r="G38" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="E38" s="32" t="s">
+      <c r="I38" s="32" t="s">
         <v>474</v>
       </c>
-      <c r="F38" s="32" t="s">
+      <c r="J38" s="32" t="s">
         <v>475</v>
       </c>
-      <c r="G38" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="I38" s="32" t="s">
-        <v>477</v>
-      </c>
-      <c r="J38" s="32" t="s">
-        <v>478</v>
-      </c>
       <c r="K38" s="25" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="L38" s="32"/>
       <c r="M38" s="32" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="42" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B39" s="32"/>
       <c r="C39" s="34"/>
@@ -6782,475 +7278,475 @@
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
       <c r="H39" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="I39" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="J39" s="32" t="s">
+        <v>480</v>
+      </c>
+      <c r="K39" s="38" t="s">
         <v>481</v>
-      </c>
-      <c r="I39" s="32" t="s">
-        <v>482</v>
-      </c>
-      <c r="J39" s="32" t="s">
-        <v>483</v>
-      </c>
-      <c r="K39" s="38" t="s">
-        <v>484</v>
       </c>
       <c r="L39" s="32"/>
       <c r="M39" s="32"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B40" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>483</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" s="32" t="s">
+        <v>484</v>
+      </c>
+      <c r="F40" s="32" t="s">
         <v>485</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="G40" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="D40" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="E40" s="32" t="s">
+      <c r="I40" s="32" t="s">
         <v>487</v>
       </c>
-      <c r="F40" s="32" t="s">
+      <c r="J40" s="32" t="s">
+        <v>484</v>
+      </c>
+      <c r="K40" s="25" t="s">
         <v>488</v>
-      </c>
-      <c r="G40" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="I40" s="32" t="s">
-        <v>490</v>
-      </c>
-      <c r="J40" s="32" t="s">
-        <v>487</v>
-      </c>
-      <c r="K40" s="25" t="s">
-        <v>491</v>
       </c>
       <c r="L40" s="32"/>
       <c r="M40" s="32" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B41" s="32" t="s">
+        <v>490</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="E41" s="32" t="s">
+        <v>491</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>492</v>
+      </c>
+      <c r="G41" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="C41" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="D41" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="E41" s="32" t="s">
+      <c r="I41" s="32" t="s">
         <v>494</v>
       </c>
-      <c r="F41" s="32" t="s">
+      <c r="J41" s="55" t="s">
         <v>495</v>
       </c>
-      <c r="G41" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H41" s="1" t="s">
+      <c r="K41" s="38" t="s">
         <v>496</v>
-      </c>
-      <c r="I41" s="32" t="s">
-        <v>497</v>
-      </c>
-      <c r="J41" s="55" t="s">
-        <v>498</v>
-      </c>
-      <c r="K41" s="38" t="s">
-        <v>499</v>
       </c>
       <c r="L41" s="32"/>
       <c r="M41" s="32"/>
     </row>
     <row r="42" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C42" s="32" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E42" s="32" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F42" s="32" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G42" s="32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H42" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="I42" s="32" t="s">
+        <v>494</v>
+      </c>
+      <c r="J42" s="55" t="s">
+        <v>495</v>
+      </c>
+      <c r="K42" s="38" t="s">
         <v>496</v>
-      </c>
-      <c r="I42" s="32" t="s">
-        <v>497</v>
-      </c>
-      <c r="J42" s="55" t="s">
-        <v>498</v>
-      </c>
-      <c r="K42" s="38" t="s">
-        <v>499</v>
       </c>
       <c r="L42" s="32"/>
       <c r="M42" s="32"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B43" s="32" t="s">
+        <v>500</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E43" s="32" t="s">
+        <v>501</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>502</v>
+      </c>
+      <c r="G43" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="C43" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="D43" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="E43" s="32" t="s">
+      <c r="I43" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="F43" s="32" t="s">
-        <v>505</v>
-      </c>
-      <c r="G43" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="I43" s="32" t="s">
-        <v>507</v>
-      </c>
       <c r="J43" s="32" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K43" s="25" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="L43" s="32"/>
       <c r="M43" s="32"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B44" s="32" t="s">
+        <v>505</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>506</v>
+      </c>
+      <c r="E44" s="32" t="s">
+        <v>507</v>
+      </c>
+      <c r="F44" s="32" t="s">
         <v>508</v>
       </c>
-      <c r="C44" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="D44" s="32" t="s">
+      <c r="G44" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="I44" s="32" t="s">
         <v>510</v>
       </c>
-      <c r="F44" s="32" t="s">
-        <v>511</v>
-      </c>
-      <c r="G44" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="I44" s="32" t="s">
-        <v>513</v>
-      </c>
       <c r="J44" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="K44" s="25" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="L44" s="32"/>
       <c r="M44" s="32"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B45" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>512</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>513</v>
+      </c>
+      <c r="G45" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="C45" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="D45" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="E45" s="32" t="s">
+      <c r="I45" s="32" t="s">
         <v>515</v>
       </c>
-      <c r="F45" s="32" t="s">
+      <c r="J45" s="32" t="s">
+        <v>512</v>
+      </c>
+      <c r="K45" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="L45" s="32" t="s">
         <v>516</v>
-      </c>
-      <c r="G45" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="I45" s="32" t="s">
-        <v>518</v>
-      </c>
-      <c r="J45" s="32" t="s">
-        <v>515</v>
-      </c>
-      <c r="K45" s="25" t="s">
-        <v>491</v>
-      </c>
-      <c r="L45" s="32" t="s">
-        <v>519</v>
       </c>
       <c r="M45" s="32"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B46" s="32" t="s">
+        <v>517</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>518</v>
+      </c>
+      <c r="E46" s="32" t="s">
+        <v>519</v>
+      </c>
+      <c r="F46" s="32" t="s">
         <v>520</v>
       </c>
-      <c r="C46" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>521</v>
-      </c>
-      <c r="E46" s="32" t="s">
-        <v>522</v>
-      </c>
-      <c r="F46" s="32" t="s">
-        <v>523</v>
-      </c>
       <c r="G46" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H46" s="32"/>
       <c r="I46" s="32" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J46" s="38" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K46" s="38" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="L46" s="32" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="M46" s="32" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B47" s="32" t="s">
+        <v>524</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="E47" s="32" t="s">
+        <v>525</v>
+      </c>
+      <c r="F47" s="32" t="s">
+        <v>526</v>
+      </c>
+      <c r="G47" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C47" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="E47" s="32" t="s">
+      <c r="I47" s="32" t="s">
         <v>528</v>
       </c>
-      <c r="F47" s="32" t="s">
-        <v>529</v>
-      </c>
-      <c r="G47" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="I47" s="32" t="s">
-        <v>531</v>
-      </c>
       <c r="J47" s="32" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="K47" s="25" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="L47" s="32"/>
       <c r="M47" s="32"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C48" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D48" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="E48" s="32" t="s">
+        <v>531</v>
+      </c>
+      <c r="F48" s="32" t="s">
+        <v>532</v>
+      </c>
+      <c r="G48" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="E48" s="32" t="s">
+      <c r="I48" s="32" t="s">
         <v>534</v>
       </c>
-      <c r="F48" s="32" t="s">
-        <v>535</v>
-      </c>
-      <c r="G48" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="I48" s="32" t="s">
-        <v>537</v>
-      </c>
       <c r="J48" s="32" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="K48" s="25" t="s">
-        <v>491</v>
-      </c>
-      <c r="L48" s="32" t="s">
-        <v>453</v>
+        <v>488</v>
+      </c>
+      <c r="L48" s="78" t="s">
+        <v>450</v>
       </c>
       <c r="M48" s="32"/>
     </row>
     <row r="49" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C49" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D49" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="E49" s="32" t="s">
+        <v>537</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>538</v>
+      </c>
+      <c r="G49" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H49" s="40" t="s">
         <v>539</v>
       </c>
-      <c r="E49" s="32" t="s">
+      <c r="I49" s="32" t="s">
         <v>540</v>
-      </c>
-      <c r="F49" s="32" t="s">
-        <v>541</v>
-      </c>
-      <c r="G49" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H49" s="40" t="s">
-        <v>542</v>
-      </c>
-      <c r="I49" s="32" t="s">
-        <v>543</v>
       </c>
       <c r="J49" s="32"/>
       <c r="K49" s="43" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="L49" s="32"/>
       <c r="M49" s="32"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C50" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D50" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="E50" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="F50" s="32" t="s">
+        <v>545</v>
+      </c>
+      <c r="G50" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="E50" s="32" t="s">
+      <c r="I50" s="32" t="s">
         <v>547</v>
       </c>
-      <c r="F50" s="32" t="s">
+      <c r="J50" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="K50" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="L50" s="78" t="s">
         <v>548</v>
-      </c>
-      <c r="G50" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="I50" s="32" t="s">
-        <v>550</v>
-      </c>
-      <c r="J50" s="32" t="s">
-        <v>547</v>
-      </c>
-      <c r="K50" s="25" t="s">
-        <v>491</v>
-      </c>
-      <c r="L50" s="32" t="s">
-        <v>551</v>
       </c>
       <c r="M50" s="32"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C51" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D51" s="32" t="s">
+        <v>550</v>
+      </c>
+      <c r="E51" s="32" t="s">
+        <v>551</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>552</v>
+      </c>
+      <c r="G51" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="E51" s="32" t="s">
+      <c r="I51" s="32" t="s">
         <v>554</v>
-      </c>
-      <c r="F51" s="32" t="s">
-        <v>555</v>
-      </c>
-      <c r="G51" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I51" s="32" t="s">
-        <v>557</v>
       </c>
       <c r="J51" s="32"/>
       <c r="K51" s="38" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="L51" s="77" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="M51" s="32"/>
     </row>
     <row r="52" spans="1:13" s="47" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="48" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B52" s="44"/>
       <c r="C52" s="44"/>
@@ -7258,539 +7754,539 @@
       <c r="E52" s="44"/>
       <c r="F52" s="44"/>
       <c r="G52" s="45" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H52" s="44"/>
       <c r="I52" s="44" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J52" s="66" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K52" s="26" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L52" s="44"/>
       <c r="M52" s="44"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B53" s="32" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C53" s="32" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E53" s="32" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>64</v>
       </c>
       <c r="G53" s="32"/>
       <c r="H53" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="I53" s="32" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="J53" s="38" t="s">
+        <v>560</v>
+      </c>
+      <c r="K53" s="38" t="s">
         <v>563</v>
-      </c>
-      <c r="K53" s="38" t="s">
-        <v>566</v>
       </c>
       <c r="L53" s="32"/>
       <c r="M53" s="32"/>
     </row>
     <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C54" s="32" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E54" s="32" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F54" s="32" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H54" s="32"/>
       <c r="I54" s="32" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J54" s="65" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="L54" s="32"/>
       <c r="M54" s="32"/>
     </row>
     <row r="55" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B55" s="32" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C55" s="32" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E55" s="32" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="F55" s="38" t="s">
         <v>64</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H55" s="32"/>
       <c r="I55" s="32" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J55" s="65" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="L55" s="32"/>
       <c r="M55" s="32"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B56" s="32" t="s">
+        <v>570</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E56" s="32" t="s">
+        <v>571</v>
+      </c>
+      <c r="F56" s="33" t="s">
+        <v>572</v>
+      </c>
+      <c r="G56" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C56" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="D56" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="E56" s="32" t="s">
+      <c r="I56" s="32" t="s">
         <v>574</v>
       </c>
-      <c r="F56" s="33" t="s">
+      <c r="J56" s="38" t="s">
+        <v>571</v>
+      </c>
+      <c r="K56" s="25" t="s">
         <v>575</v>
-      </c>
-      <c r="G56" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="I56" s="32" t="s">
-        <v>577</v>
-      </c>
-      <c r="J56" s="38" t="s">
-        <v>574</v>
-      </c>
-      <c r="K56" s="25" t="s">
-        <v>578</v>
       </c>
       <c r="L56" s="32"/>
       <c r="M56" s="32"/>
     </row>
     <row r="57" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B57" s="32" t="s">
+        <v>576</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="D57" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="E57" s="32" t="s">
+        <v>577</v>
+      </c>
+      <c r="F57" s="32" t="s">
+        <v>578</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I57" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="J57" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="K57" s="26" t="s">
         <v>579</v>
-      </c>
-      <c r="C57" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="D57" s="32" t="s">
-        <v>269</v>
-      </c>
-      <c r="E57" s="32" t="s">
-        <v>580</v>
-      </c>
-      <c r="F57" s="32" t="s">
-        <v>581</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="I57" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="J57" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="K57" s="26" t="s">
-        <v>582</v>
       </c>
       <c r="M57" s="32"/>
     </row>
     <row r="58" spans="1:13" s="2" customFormat="1" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B58" s="49" t="s">
         <v>65</v>
       </c>
       <c r="C58" s="50" t="s">
+        <v>580</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F58" s="59" t="s">
+        <v>582</v>
+      </c>
+      <c r="G58" s="51" t="s">
         <v>583</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="I58" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="F58" s="59" t="s">
-        <v>585</v>
-      </c>
-      <c r="G58" s="51" t="s">
-        <v>586</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>587</v>
       </c>
       <c r="J58" s="39"/>
       <c r="K58" s="39" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C59" s="32" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E59" s="32" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>64</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H59" s="32"/>
       <c r="I59" s="32" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="J59" s="38" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="L59" s="32"/>
       <c r="M59" s="32"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B60" s="32" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C60" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="E60" s="32" t="s">
+      <c r="F60" s="32" t="s">
+        <v>590</v>
+      </c>
+      <c r="G60" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F60" s="32" t="s">
-        <v>593</v>
-      </c>
-      <c r="G60" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H60" s="1" t="s">
+      <c r="I60" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="I60" s="32" t="s">
-        <v>102</v>
-      </c>
       <c r="J60" s="32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K60" s="25" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="L60" s="32" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="M60" s="32"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C61" s="32" t="s">
+        <v>359</v>
+      </c>
+      <c r="D61" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="E61" s="32" t="s">
+        <v>594</v>
+      </c>
+      <c r="F61" s="32" t="s">
+        <v>595</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="D61" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E61" s="32" t="s">
-        <v>597</v>
-      </c>
-      <c r="F61" s="32" t="s">
-        <v>598</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="H61" s="32"/>
       <c r="I61" s="32" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="J61" s="38" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="K61" s="38" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="L61" s="32" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="M61" s="32"/>
     </row>
     <row r="62" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C62" s="32" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E62" s="32" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F62" s="32" t="s">
         <v>64</v>
       </c>
       <c r="G62" s="32"/>
       <c r="H62" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I62" s="32" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="J62" s="38" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="L62" s="32"/>
       <c r="M62" s="32"/>
     </row>
     <row r="63" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B63" s="32" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C63" s="32" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E63" s="32" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F63" s="32" t="s">
         <v>64</v>
       </c>
       <c r="G63" s="32"/>
       <c r="H63" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I63" s="32" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="J63" s="38" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K63" s="25" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="L63" s="32"/>
       <c r="M63" s="32"/>
     </row>
     <row r="64" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B64" s="32" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E64" s="32" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="G64" s="32"/>
       <c r="H64" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J64" s="32" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="K64" s="25" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="L64" s="32" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="M64" s="32"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B65" s="32" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C65" s="32" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E65" s="32" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="G65" s="32"/>
       <c r="H65" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I65" s="32" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="J65" s="32" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="K65" s="25" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="L65" s="32" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="M65" s="32"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B66" s="32" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C66" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="D66" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" s="32" t="s">
+        <v>396</v>
+      </c>
+      <c r="F66" s="32" t="s">
+        <v>607</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D66" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="E66" s="32" t="s">
+      <c r="I66" s="32" t="s">
         <v>399</v>
-      </c>
-      <c r="F66" s="32" t="s">
-        <v>610</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I66" s="32" t="s">
-        <v>402</v>
       </c>
       <c r="J66" s="32"/>
       <c r="K66" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="L66" s="32" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="M66" s="32"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B67" s="32" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C67" s="32" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D67" s="32" t="s">
         <v>29</v>
       </c>
       <c r="E67" s="32" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>32</v>
@@ -7800,31 +8296,31 @@
       </c>
       <c r="J67" s="32"/>
       <c r="K67" s="25" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="L67" s="32" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="M67" s="32"/>
     </row>
     <row r="68" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B68" s="32" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C68" s="32" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E68" s="32" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F68" s="38" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>40</v>
@@ -7837,130 +8333,130 @@
         <v>42</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="L68" s="32" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="M68" s="32"/>
     </row>
     <row r="69" spans="1:14" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B69" s="32" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C69" s="32" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D69" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="E69" s="32" t="s">
+        <v>619</v>
+      </c>
+      <c r="F69" s="32" t="s">
+        <v>620</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="E69" s="32" t="s">
-        <v>622</v>
-      </c>
-      <c r="F69" s="32" t="s">
-        <v>623</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="H69" s="32"/>
       <c r="I69" s="32" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="J69" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="K69" s="38" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="L69" s="32" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="M69" s="32"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C70" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E70" s="32" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="G70" s="32"/>
       <c r="H70" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I70" s="32" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="J70" s="32" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K70" s="25" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="L70" s="32" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="M70" s="32"/>
     </row>
     <row r="71" spans="1:14" s="47" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="44" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B71" s="44" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C71" s="44" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D71" s="44" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E71" s="63" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F71" s="48" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="G71" s="52"/>
       <c r="H71" s="45" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="I71" s="53" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="J71" s="63" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K71" s="26" t="s">
-        <v>627</v>
-      </c>
-      <c r="L71" s="44" t="s">
-        <v>634</v>
+        <v>624</v>
+      </c>
+      <c r="L71" s="78" t="s">
+        <v>631</v>
       </c>
       <c r="M71" s="44"/>
     </row>
     <row r="72" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C72" s="32" t="s">
         <v>53</v>
@@ -7969,203 +8465,203 @@
         <v>92</v>
       </c>
       <c r="E72" s="32" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="G72" s="32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I72" s="32" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="J72" s="55" t="s">
         <v>93</v>
       </c>
       <c r="K72" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="L72" s="32" t="s">
-        <v>638</v>
+        <v>591</v>
+      </c>
+      <c r="L72" s="44" t="s">
+        <v>635</v>
       </c>
       <c r="M72" s="32"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B73" s="32" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C73" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="E73" s="32" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F73" s="32" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G73" s="32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H73" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="I73" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="J73" s="32" t="s">
+        <v>449</v>
+      </c>
+      <c r="K73" s="25" t="s">
+        <v>591</v>
+      </c>
+      <c r="L73" s="78" t="s">
         <v>450</v>
-      </c>
-      <c r="I73" s="32" t="s">
-        <v>451</v>
-      </c>
-      <c r="J73" s="32" t="s">
-        <v>452</v>
-      </c>
-      <c r="K73" s="25" t="s">
-        <v>594</v>
-      </c>
-      <c r="L73" s="32" t="s">
-        <v>453</v>
       </c>
       <c r="M73" s="32"/>
     </row>
     <row r="74" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B74" s="32" t="s">
+        <v>640</v>
+      </c>
+      <c r="C74" s="32" t="s">
+        <v>641</v>
+      </c>
+      <c r="D74" s="32" t="s">
+        <v>453</v>
+      </c>
+      <c r="E74" s="32" t="s">
+        <v>642</v>
+      </c>
+      <c r="F74" s="32" t="s">
         <v>643</v>
       </c>
-      <c r="C74" s="32" t="s">
-        <v>644</v>
-      </c>
-      <c r="D74" s="32" t="s">
+      <c r="G74" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="E74" s="32" t="s">
-        <v>645</v>
-      </c>
-      <c r="F74" s="32" t="s">
-        <v>646</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="H74" s="32"/>
       <c r="I74" s="32" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="J74" s="38" t="s">
+        <v>642</v>
+      </c>
+      <c r="K74" s="38" t="s">
         <v>645</v>
-      </c>
-      <c r="K74" s="38" t="s">
-        <v>648</v>
       </c>
       <c r="L74" s="32"/>
       <c r="M74" s="32"/>
     </row>
     <row r="75" spans="1:14" s="56" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="56" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B75" s="32" t="s">
         <v>65</v>
       </c>
       <c r="C75" s="32"/>
       <c r="D75" s="56" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="56" t="s">
+        <v>647</v>
+      </c>
+      <c r="G75" s="57" t="s">
+        <v>648</v>
+      </c>
+      <c r="I75" s="56" t="s">
+        <v>649</v>
+      </c>
+      <c r="J75" s="54" t="s">
         <v>650</v>
       </c>
-      <c r="G75" s="57" t="s">
+      <c r="K75" s="58" t="s">
         <v>651</v>
-      </c>
-      <c r="I75" s="56" t="s">
-        <v>652</v>
-      </c>
-      <c r="J75" s="54" t="s">
-        <v>653</v>
-      </c>
-      <c r="K75" s="58" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="76" spans="1:14" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C76" s="32" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D76" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="E76" s="32" t="s">
+        <v>653</v>
+      </c>
+      <c r="F76" s="32" t="s">
+        <v>654</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="E76" s="32" t="s">
-        <v>656</v>
-      </c>
-      <c r="F76" s="32" t="s">
-        <v>657</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="H76" s="32"/>
       <c r="I76" s="61" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J76" s="60" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>619</v>
-      </c>
-      <c r="L76" s="32" t="s">
-        <v>658</v>
+        <v>616</v>
+      </c>
+      <c r="L76" s="44" t="s">
+        <v>655</v>
       </c>
       <c r="M76" s="32"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B77" s="32" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C77" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D77" s="32" t="s">
+        <v>470</v>
+      </c>
+      <c r="E77" s="32" t="s">
+        <v>657</v>
+      </c>
+      <c r="F77" s="32" t="s">
+        <v>658</v>
+      </c>
+      <c r="G77" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="H77" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="E77" s="32" t="s">
-        <v>660</v>
-      </c>
-      <c r="F77" s="32" t="s">
-        <v>661</v>
-      </c>
-      <c r="G77" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="I77" s="32" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="J77" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="K77" s="25" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="L77" s="32"/>
       <c r="M77" s="32"/>
@@ -8559,14 +9055,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.77734375" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
     <col min="2" max="2" width="39.44140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.44140625" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="39.44140625" style="1" customWidth="1"/>
     <col min="11" max="11" width="20.88671875" customWidth="1"/>
     <col min="12" max="12" width="41.6640625" style="47" customWidth="1"/>
@@ -8574,28 +9070,28 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="L1" s="48"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C2" s="10"/>
       <c r="E2" s="10"/>
@@ -8603,190 +9099,190 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="E3" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="L3" s="52"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>660</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C4" t="s">
+        <v>664</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="E4" t="s">
         <v>663</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="C4" t="s">
-        <v>667</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="E4" t="s">
-        <v>666</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="L4" s="52"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E5" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="L5" s="52"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E6" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="L6" s="52"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C7" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L7" s="52"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C8" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="L8" s="52"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C9" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="L9" s="52"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C10" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="E10" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="L10" s="52"/>
     </row>
     <row r="11" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C11" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L11" s="52"/>
     </row>
@@ -8796,254 +9292,254 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E14" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E15" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C16" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E16" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C17" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E17" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C18" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E18" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E19" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E20" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="47" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D21" s="45" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F21" s="45" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L21" s="46"/>
     </row>
     <row r="22" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="47" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D22" s="45" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="L22" s="46"/>
     </row>
     <row r="23" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D23" s="45" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F23" s="45" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="L23" s="52"/>
     </row>
     <row r="24" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D24" s="45" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F24" s="45" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="L24" s="52"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="L25" s="52"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C26" s="32" t="s">
         <v>33</v>
@@ -9055,16 +9551,16 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C27" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E27" t="s">
         <v>41</v>
@@ -9075,367 +9571,367 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C28" t="s">
+        <v>697</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="E28" t="s">
+        <v>699</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="E28" t="s">
-        <v>702</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C29" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E29" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C30" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E30" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="E31" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C32" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E32" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="L32" s="46"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C33" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E33" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C34" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E34" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C35" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E35" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C38" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E38" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="L38" s="44"/>
       <c r="M38" s="32"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C39" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E39" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L39" s="44"/>
       <c r="M39" s="32"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C40" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E40" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L40" s="52"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C41" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E41" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="L41" s="52"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C42" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E42" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L42" s="52"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C43" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E43" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L43" s="52"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C44" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E44" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="L44" s="46"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C45" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="L45" s="52"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="32" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C46" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E46" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L46" s="52"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="L47" s="46"/>
     </row>
@@ -9445,257 +9941,257 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="48" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="L49" s="44"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C50" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E50" s="32" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="L50" s="44"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C51" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E51" s="32" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="L51" s="44"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C52" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C53" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E53" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C54" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B55" s="45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D55" s="45" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F55" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B56" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D56" s="45" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E56" s="47" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F56" s="45" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B57" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C57" s="47" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D57" s="45" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E57" s="47" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F57" s="45" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L57" s="46"/>
     </row>
     <row r="58" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B58" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D58" s="45" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E58" s="47" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F58" s="45" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="L58" s="46"/>
     </row>
     <row r="59" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B59" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D59" s="45" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F59" s="45" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="L59" s="52"/>
     </row>
     <row r="60" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B60" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C60" s="47" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D60" s="45" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F60" s="45" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="L60" s="52"/>
     </row>
     <row r="61" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B61" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C61" s="44" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D61" s="45" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F61" s="45"/>
     </row>
     <row r="62" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B62" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C62" s="44" t="s">
         <v>33</v>
@@ -9708,16 +10204,16 @@
     </row>
     <row r="63" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B63" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C63" s="47" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D63" s="45" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E63" s="47" t="s">
         <v>41</v>
@@ -9729,283 +10225,688 @@
     </row>
     <row r="64" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="47" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B64" s="45" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C64" s="47" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D64" s="45" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F64" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="47" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B65" s="45" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C65" s="47" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D65" s="45" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F65" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="47" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B66" s="45" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C66" s="47" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D66" s="45" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F66" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="47" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B67" s="45" t="s">
         <v>95</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D67" s="45" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F67" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C68" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E68" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="L68" s="46"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C69" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E69" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="70" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="47" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B70" s="45" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D70" s="45" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F70" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="47" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="47" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B71" s="45" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C71" s="47" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D71" s="45" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F71" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L72" s="46"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>288</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C74" t="s">
+        <v>735</v>
+      </c>
       <c r="L74" s="46"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>288</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C75" t="s">
+        <v>735</v>
+      </c>
+      <c r="E75" t="s">
+        <v>738</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>736</v>
+      </c>
       <c r="L75" s="46"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>288</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C76" t="s">
+        <v>735</v>
+      </c>
+      <c r="E76" t="s">
+        <v>740</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>737</v>
+      </c>
       <c r="L76" s="46"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E77" t="s">
+        <v>741</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>739</v>
+      </c>
       <c r="L77" s="44"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L78" s="44"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L79" s="46"/>
+      <c r="A79" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C79" t="s">
+        <v>742</v>
+      </c>
+      <c r="E79" t="s">
+        <v>743</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="L79" s="52"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L80" s="52"/>
-    </row>
-    <row r="81" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C80" t="s">
+        <v>742</v>
+      </c>
+      <c r="E80" t="s">
+        <v>744</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="L80" s="44"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C81" t="s">
+        <v>742</v>
+      </c>
+      <c r="E81" t="s">
+        <v>745</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>764</v>
+      </c>
       <c r="L81" s="44"/>
     </row>
-    <row r="82" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C82" t="s">
+        <v>742</v>
+      </c>
+      <c r="E82" t="s">
+        <v>746</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>765</v>
+      </c>
       <c r="L82" s="44"/>
     </row>
-    <row r="83" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C83" t="s">
+        <v>742</v>
+      </c>
+      <c r="E83" t="s">
+        <v>747</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>763</v>
+      </c>
       <c r="L83" s="44"/>
     </row>
-    <row r="84" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L84" s="44"/>
-    </row>
-    <row r="85" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C84" t="s">
+        <v>742</v>
+      </c>
+      <c r="E84" t="s">
+        <v>748</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="L84" s="46"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C85" t="s">
+        <v>742</v>
+      </c>
+      <c r="E85" t="s">
+        <v>749</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>768</v>
+      </c>
       <c r="L85" s="46"/>
     </row>
-    <row r="86" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C86" t="s">
+        <v>742</v>
+      </c>
+      <c r="E86" t="s">
+        <v>750</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>761</v>
+      </c>
       <c r="L86" s="46"/>
     </row>
-    <row r="87" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C87" t="s">
+        <v>742</v>
+      </c>
+      <c r="E87" t="s">
+        <v>751</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>767</v>
+      </c>
       <c r="L87" s="46"/>
     </row>
-    <row r="88" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C88" t="s">
+        <v>742</v>
+      </c>
+      <c r="E88" t="s">
+        <v>785</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>787</v>
+      </c>
       <c r="L88" s="46"/>
     </row>
-    <row r="89" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L89" s="46"/>
     </row>
-    <row r="90" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L90" s="46"/>
     </row>
-    <row r="91" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>304</v>
+      </c>
+      <c r="B91" t="s">
+        <v>303</v>
+      </c>
+      <c r="C91" t="s">
+        <v>735</v>
+      </c>
+      <c r="E91" s="32" t="s">
+        <v>752</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>773</v>
+      </c>
       <c r="L91" s="46"/>
     </row>
-    <row r="92" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>304</v>
+      </c>
+      <c r="B92" t="s">
+        <v>303</v>
+      </c>
+      <c r="C92" t="s">
+        <v>735</v>
+      </c>
+      <c r="E92" t="s">
+        <v>753</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>772</v>
+      </c>
       <c r="L92" s="46"/>
     </row>
-    <row r="93" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>304</v>
+      </c>
+      <c r="B93" t="s">
+        <v>303</v>
+      </c>
+      <c r="C93" t="s">
+        <v>735</v>
+      </c>
+      <c r="E93" t="s">
+        <v>754</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>774</v>
+      </c>
       <c r="L93" s="46"/>
     </row>
-    <row r="94" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>304</v>
+      </c>
+      <c r="B94" t="s">
+        <v>303</v>
+      </c>
+      <c r="C94" t="s">
+        <v>735</v>
+      </c>
+      <c r="E94" t="s">
+        <v>755</v>
+      </c>
+      <c r="F94" t="s">
+        <v>775</v>
+      </c>
       <c r="L94" s="46"/>
     </row>
-    <row r="95" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>304</v>
+      </c>
+      <c r="B95" t="s">
+        <v>303</v>
+      </c>
+      <c r="C95" t="s">
+        <v>735</v>
+      </c>
+      <c r="E95" t="s">
+        <v>756</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>776</v>
+      </c>
       <c r="L95" s="46"/>
     </row>
-    <row r="96" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>304</v>
+      </c>
+      <c r="B96" t="s">
+        <v>303</v>
+      </c>
+      <c r="C96" t="s">
+        <v>735</v>
+      </c>
+      <c r="E96" t="s">
+        <v>771</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>777</v>
+      </c>
       <c r="L96" s="46"/>
     </row>
-    <row r="97" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>304</v>
+      </c>
+      <c r="B97" t="s">
+        <v>303</v>
+      </c>
+      <c r="C97" t="s">
+        <v>735</v>
+      </c>
+      <c r="E97" t="s">
+        <v>757</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>778</v>
+      </c>
       <c r="L97" s="46"/>
     </row>
-    <row r="98" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>304</v>
+      </c>
+      <c r="B98" t="s">
+        <v>303</v>
+      </c>
+      <c r="C98" t="s">
+        <v>735</v>
+      </c>
+      <c r="E98" t="s">
+        <v>770</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>779</v>
+      </c>
       <c r="L98" s="46"/>
     </row>
-    <row r="99" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>304</v>
+      </c>
+      <c r="B99" t="s">
+        <v>303</v>
+      </c>
+      <c r="C99" t="s">
+        <v>735</v>
+      </c>
+      <c r="E99" t="s">
+        <v>758</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>780</v>
+      </c>
       <c r="L99" s="46"/>
     </row>
-    <row r="100" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>304</v>
+      </c>
+      <c r="B100" t="s">
+        <v>303</v>
+      </c>
+      <c r="C100" t="s">
+        <v>735</v>
+      </c>
+      <c r="E100" t="s">
+        <v>759</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>781</v>
+      </c>
       <c r="L100" s="46"/>
     </row>
-    <row r="101" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>304</v>
+      </c>
+      <c r="B101" t="s">
+        <v>303</v>
+      </c>
+      <c r="C101" t="s">
+        <v>735</v>
+      </c>
+      <c r="E101" t="s">
+        <v>760</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>782</v>
+      </c>
       <c r="L101" s="46"/>
     </row>
-    <row r="102" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L102" s="46"/>
     </row>
-    <row r="103" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L103" s="66"/>
-    </row>
-    <row r="104" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>312</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C103" t="s">
+        <v>742</v>
+      </c>
+      <c r="L103" s="46"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>312</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C104" t="s">
+        <v>742</v>
+      </c>
+      <c r="E104" t="s">
+        <v>784</v>
+      </c>
+      <c r="F104" t="s">
+        <v>783</v>
+      </c>
       <c r="L104" s="66"/>
     </row>
-    <row r="105" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>312</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C105" t="s">
+        <v>742</v>
+      </c>
+      <c r="E105" t="s">
+        <v>788</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>786</v>
+      </c>
       <c r="L105" s="66"/>
     </row>
-    <row r="106" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L106" s="46"/>
-    </row>
-    <row r="107" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L107" s="52"/>
-    </row>
-    <row r="108" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E106" t="s">
+        <v>785</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="L106" s="66"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L107" s="46"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L108" s="52"/>
     </row>
-    <row r="109" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L109" s="46"/>
-    </row>
-    <row r="110" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L109" s="52"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L110" s="46"/>
     </row>
-    <row r="111" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L111" s="46"/>
     </row>
-    <row r="112" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L112" s="46"/>
     </row>
     <row r="113" spans="12:12" x14ac:dyDescent="0.3">
@@ -10015,22 +10916,25 @@
       <c r="L114" s="46"/>
     </row>
     <row r="115" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L115" s="44"/>
+      <c r="L115" s="46"/>
     </row>
     <row r="116" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L116" s="76"/>
+      <c r="L116" s="44"/>
     </row>
     <row r="117" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L117" s="44"/>
+      <c r="L117" s="76"/>
     </row>
     <row r="118" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L118" s="46"/>
+      <c r="L118" s="44"/>
     </row>
     <row r="119" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L119" s="52"/>
+      <c r="L119" s="46"/>
     </row>
     <row r="120" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L120" s="46"/>
+      <c r="L120" s="52"/>
+    </row>
+    <row r="121" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L121" s="46"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10055,8 +10959,20 @@
     <hyperlink ref="D61" r:id="rId19"/>
     <hyperlink ref="D62" r:id="rId20"/>
     <hyperlink ref="F33" r:id="rId21"/>
+    <hyperlink ref="B75" r:id="rId22"/>
+    <hyperlink ref="B76" r:id="rId23"/>
+    <hyperlink ref="B79" r:id="rId24"/>
+    <hyperlink ref="B80" r:id="rId25"/>
+    <hyperlink ref="B81" r:id="rId26"/>
+    <hyperlink ref="B83" r:id="rId27"/>
+    <hyperlink ref="B85" r:id="rId28"/>
+    <hyperlink ref="B87" r:id="rId29"/>
+    <hyperlink ref="B82" r:id="rId30"/>
+    <hyperlink ref="B84" r:id="rId31"/>
+    <hyperlink ref="B86" r:id="rId32"/>
+    <hyperlink ref="B88" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId34"/>
 </worksheet>
 </file>
--- a/ΟΒΙΒv2.2/Biobank, Collection, Network, Research Resource(v2.2).xlsx
+++ b/ΟΒΙΒv2.2/Biobank, Collection, Network, Research Resource(v2.2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="sample,sample donor,event(v2.1)" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="919">
   <si>
     <t>Entity</t>
   </si>
@@ -2677,6 +2677,396 @@
   </si>
   <si>
     <t>ISO 9001</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002042</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002054</t>
+  </si>
+  <si>
+    <t>biochemical dataset</t>
+  </si>
+  <si>
+    <t>body (radiological) image</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002044</t>
+  </si>
+  <si>
+    <t>clinical dataset</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002040</t>
+  </si>
+  <si>
+    <t>environmental dataset</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002057</t>
+  </si>
+  <si>
+    <t>genealogical records</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002043</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002039</t>
+  </si>
+  <si>
+    <t>lifestyle dataset</t>
+  </si>
+  <si>
+    <t>genomic dataset</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002053</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0000679</t>
+  </si>
+  <si>
+    <t>metabolomic dataset</t>
+  </si>
+  <si>
+    <t>patient registry data</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002056</t>
+  </si>
+  <si>
+    <t>photo image</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002041</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002052</t>
+  </si>
+  <si>
+    <t>proteomic dataset</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002046</t>
+  </si>
+  <si>
+    <t>psychological dataset</t>
+  </si>
+  <si>
+    <t>physiological dataset</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/obib.owl/OBIB_0002055</t>
+  </si>
+  <si>
+    <t>whole slide image</t>
+  </si>
+  <si>
+    <t>Routine health care setting</t>
+  </si>
+  <si>
+    <t>Clinical trial</t>
+  </si>
+  <si>
+    <t>Research study</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Case-control</t>
+  </si>
+  <si>
+    <t>Longitudinal cohort</t>
+  </si>
+  <si>
+    <t>Twin-study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-sectional </t>
+  </si>
+  <si>
+    <t>Quality control study</t>
+  </si>
+  <si>
+    <t>Population-based cohort</t>
+  </si>
+  <si>
+    <t>Reference collection</t>
+  </si>
+  <si>
+    <t>disease collection</t>
+  </si>
+  <si>
+    <t>Birth cohort</t>
+  </si>
+  <si>
+    <t>Microbial collection (if applicable with resistance data)</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Disease-specific cohort</t>
+  </si>
+  <si>
+    <t>subclass</t>
+  </si>
+  <si>
+    <t>Public health or population based study</t>
+  </si>
+  <si>
+    <t>Museum collection</t>
+  </si>
+  <si>
+    <t>archeological collection</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002116</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002115</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002114</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002113</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002112</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002099</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002128</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002127</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002125</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002126</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002124</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002123</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002122</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002121</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002120</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002119</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002118</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002117</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Ended</t>
+  </si>
+  <si>
+    <t>collection or research resource status</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002129</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002130</t>
+  </si>
+  <si>
+    <t>Inclusion criterion</t>
+  </si>
+  <si>
+    <t>Use of medication inclusion criterion</t>
+  </si>
+  <si>
+    <t>Gravidity inclusion criterion</t>
+  </si>
+  <si>
+    <t>Age group inclusion criterion</t>
+  </si>
+  <si>
+    <t>Family status inclusion criterion</t>
+  </si>
+  <si>
+    <t>Sex inclusion criterion</t>
+  </si>
+  <si>
+    <t>Country of residence inclusion criteria</t>
+  </si>
+  <si>
+    <t>Ethnicity inclusion criterion</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002460</t>
+  </si>
+  <si>
+    <t>Defined population inclusion criterion</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002454</t>
+  </si>
+  <si>
+    <t>Clinically relevant lifestyle inclusion criterion</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002455</t>
+  </si>
+  <si>
+    <t>Clinically relevant exposure inclusion criterion</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002563</t>
+  </si>
+  <si>
+    <t>Health status inclusion criterion</t>
+  </si>
+  <si>
+    <t>Hospital patient inclusion criterion</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002562</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002561</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002560</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002555</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002456</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002558</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002559</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBI_0002453</t>
+  </si>
+  <si>
+    <t>Research resource design</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002060</t>
+  </si>
+  <si>
+    <t>Common charter</t>
+  </si>
+  <si>
+    <t>Common SOPs</t>
+  </si>
+  <si>
+    <t>Common data access policy</t>
+  </si>
+  <si>
+    <t>Common sample access</t>
+  </si>
+  <si>
+    <t>Common image MTA</t>
+  </si>
+  <si>
+    <t>Common representation</t>
+  </si>
+  <si>
+    <t>Common URL</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002057</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002137</t>
+  </si>
+  <si>
+    <t>Common MTA</t>
+  </si>
+  <si>
+    <t>policy</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002136</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002138</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002139</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002135</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002134</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002133</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002132</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002131</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rare Disease network</t>
+  </si>
+  <si>
+    <t>Project network</t>
+  </si>
+  <si>
+    <t>Disease-specific network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collection network </t>
+  </si>
+  <si>
+    <t>Biobank network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBMRI-ERIC National Node network </t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002141</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002146</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002145</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002144</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002143</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OBIB_0002142</t>
+  </si>
+  <si>
+    <t>type of</t>
   </si>
 </sst>
 </file>
@@ -3020,7 +3410,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3043,12 +3433,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -3268,7 +3652,7 @@
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6884,7 +7268,7 @@
       <c r="K28" s="43" t="s">
         <v>400</v>
       </c>
-      <c r="L28" s="78" t="s">
+      <c r="L28" s="44" t="s">
         <v>401</v>
       </c>
       <c r="M28" s="32"/>
@@ -6921,7 +7305,7 @@
       <c r="K29" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="L29" s="78" t="s">
+      <c r="L29" s="77" t="s">
         <v>407</v>
       </c>
       <c r="M29" s="32"/>
@@ -7034,7 +7418,7 @@
       <c r="K32" s="25" t="s">
         <v>342</v>
       </c>
-      <c r="L32" s="78" t="s">
+      <c r="L32" s="44" t="s">
         <v>429</v>
       </c>
       <c r="M32" s="32"/>
@@ -7073,7 +7457,7 @@
       <c r="K33" s="25" t="s">
         <v>342</v>
       </c>
-      <c r="L33" s="78" t="s">
+      <c r="L33" s="44" t="s">
         <v>437</v>
       </c>
       <c r="M33" s="32"/>
@@ -7151,7 +7535,7 @@
       <c r="K35" s="25" t="s">
         <v>342</v>
       </c>
-      <c r="L35" s="78" t="s">
+      <c r="L35" s="44" t="s">
         <v>450</v>
       </c>
       <c r="M35" s="32"/>
@@ -7223,7 +7607,7 @@
       <c r="K37" s="38" t="s">
         <v>459</v>
       </c>
-      <c r="L37" s="78" t="s">
+      <c r="L37" s="44" t="s">
         <v>468</v>
       </c>
       <c r="M37" s="32"/>
@@ -7628,7 +8012,7 @@
       <c r="K48" s="25" t="s">
         <v>488</v>
       </c>
-      <c r="L48" s="78" t="s">
+      <c r="L48" s="44" t="s">
         <v>450</v>
       </c>
       <c r="M48" s="32"/>
@@ -7702,7 +8086,7 @@
       <c r="K50" s="25" t="s">
         <v>488</v>
       </c>
-      <c r="L50" s="78" t="s">
+      <c r="L50" s="44" t="s">
         <v>548</v>
       </c>
       <c r="M50" s="32"/>
@@ -7739,7 +8123,7 @@
       <c r="K51" s="38" t="s">
         <v>555</v>
       </c>
-      <c r="L51" s="77" t="s">
+      <c r="L51" s="44" t="s">
         <v>556</v>
       </c>
       <c r="M51" s="32"/>
@@ -8446,7 +8830,7 @@
       <c r="K71" s="26" t="s">
         <v>624</v>
       </c>
-      <c r="L71" s="78" t="s">
+      <c r="L71" s="44" t="s">
         <v>631</v>
       </c>
       <c r="M71" s="44"/>
@@ -8524,7 +8908,7 @@
       <c r="K73" s="25" t="s">
         <v>591</v>
       </c>
-      <c r="L73" s="78" t="s">
+      <c r="L73" s="44" t="s">
         <v>450</v>
       </c>
       <c r="M73" s="32"/>
@@ -9055,10 +9439,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M207"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
     <col min="2" max="2" width="39.44140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.44140625" style="1" customWidth="1"/>
@@ -10898,43 +11282,1390 @@
       <c r="L108" s="52"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B109"/>
+      <c r="C109" t="s">
+        <v>399</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E109" t="s">
+        <v>791</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>789</v>
+      </c>
       <c r="L109" s="52"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B110"/>
+      <c r="C110" t="s">
+        <v>399</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E110" t="s">
+        <v>792</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>790</v>
+      </c>
       <c r="L110" s="46"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B111"/>
+      <c r="C111" t="s">
+        <v>399</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E111" t="s">
+        <v>794</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>793</v>
+      </c>
       <c r="L111" s="46"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B112"/>
+      <c r="C112" t="s">
+        <v>399</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E112" t="s">
+        <v>796</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>795</v>
+      </c>
       <c r="L112" s="46"/>
     </row>
-    <row r="113" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B113"/>
+      <c r="C113" t="s">
+        <v>399</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E113" t="s">
+        <v>798</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>797</v>
+      </c>
       <c r="L113" s="46"/>
     </row>
-    <row r="114" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B114"/>
+      <c r="C114" t="s">
+        <v>399</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E114" t="s">
+        <v>802</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>799</v>
+      </c>
       <c r="L114" s="46"/>
     </row>
-    <row r="115" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B115"/>
+      <c r="C115" t="s">
+        <v>399</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E115" t="s">
+        <v>801</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>800</v>
+      </c>
       <c r="L115" s="46"/>
     </row>
-    <row r="116" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B116"/>
+      <c r="C116" t="s">
+        <v>399</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E116" t="s">
+        <v>805</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>803</v>
+      </c>
       <c r="L116" s="44"/>
     </row>
-    <row r="117" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B117"/>
+      <c r="C117" t="s">
+        <v>399</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E117" t="s">
+        <v>806</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>804</v>
+      </c>
       <c r="L117" s="76"/>
     </row>
-    <row r="118" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B118"/>
+      <c r="C118" t="s">
+        <v>399</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E118" t="s">
+        <v>808</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>807</v>
+      </c>
       <c r="L118" s="44"/>
     </row>
-    <row r="119" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B119"/>
+      <c r="C119" t="s">
+        <v>399</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E119" t="s">
+        <v>814</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>809</v>
+      </c>
       <c r="L119" s="46"/>
     </row>
-    <row r="120" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B120"/>
+      <c r="C120" t="s">
+        <v>399</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E120" t="s">
+        <v>811</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>810</v>
+      </c>
       <c r="L120" s="52"/>
     </row>
-    <row r="121" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B121"/>
+      <c r="C121" t="s">
+        <v>399</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E121" t="s">
+        <v>813</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>812</v>
+      </c>
       <c r="L121" s="46"/>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B122"/>
+      <c r="C122" t="s">
+        <v>399</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E122" t="s">
+        <v>816</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A124" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C124" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A125" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C125" t="s">
+        <v>833</v>
+      </c>
+      <c r="E125" t="s">
+        <v>817</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A126" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C126" t="s">
+        <v>833</v>
+      </c>
+      <c r="E126" t="s">
+        <v>818</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A127" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C127" t="s">
+        <v>833</v>
+      </c>
+      <c r="E127" t="s">
+        <v>819</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A128" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C128" t="s">
+        <v>833</v>
+      </c>
+      <c r="E128" t="s">
+        <v>834</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C129" t="s">
+        <v>833</v>
+      </c>
+      <c r="E129" t="s">
+        <v>835</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C130" t="s">
+        <v>833</v>
+      </c>
+      <c r="E130" t="s">
+        <v>836</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C131" t="s">
+        <v>833</v>
+      </c>
+      <c r="E131" t="s">
+        <v>820</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="32"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="32"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C135" t="s">
+        <v>718</v>
+      </c>
+      <c r="E135" t="s">
+        <v>821</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C136" t="s">
+        <v>718</v>
+      </c>
+      <c r="E136" t="s">
+        <v>824</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C137" t="s">
+        <v>718</v>
+      </c>
+      <c r="E137" t="s">
+        <v>822</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C138" t="s">
+        <v>718</v>
+      </c>
+      <c r="E138" t="s">
+        <v>823</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C139" t="s">
+        <v>718</v>
+      </c>
+      <c r="E139" t="s">
+        <v>825</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C140" t="s">
+        <v>718</v>
+      </c>
+      <c r="E140" t="s">
+        <v>826</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C141" t="s">
+        <v>718</v>
+      </c>
+      <c r="E141" t="s">
+        <v>827</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C142" t="s">
+        <v>718</v>
+      </c>
+      <c r="E142" t="s">
+        <v>832</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C143" t="s">
+        <v>718</v>
+      </c>
+      <c r="E143" t="s">
+        <v>829</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C144" t="s">
+        <v>718</v>
+      </c>
+      <c r="E144" t="s">
+        <v>828</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C145" t="s">
+        <v>718</v>
+      </c>
+      <c r="E145" s="44" t="s">
+        <v>830</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C146" t="s">
+        <v>718</v>
+      </c>
+      <c r="E146" s="44" t="s">
+        <v>831</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="32"/>
+      <c r="E147" s="44" t="s">
+        <v>785</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E148" s="44"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E149" s="44"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="78" t="s">
+        <v>857</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C150" t="s">
+        <v>718</v>
+      </c>
+      <c r="E150" s="44" t="s">
+        <v>855</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="78" t="s">
+        <v>857</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C151" t="s">
+        <v>718</v>
+      </c>
+      <c r="E151" t="s">
+        <v>856</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="32" t="s">
+        <v>857</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C152" t="s">
+        <v>718</v>
+      </c>
+      <c r="E152" s="47" t="s">
+        <v>785</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C155" t="s">
+        <v>735</v>
+      </c>
+      <c r="E155" s="44" t="s">
+        <v>875</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C156" t="s">
+        <v>735</v>
+      </c>
+      <c r="E156" s="47" t="s">
+        <v>876</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C157" t="s">
+        <v>735</v>
+      </c>
+      <c r="E157" s="47" t="s">
+        <v>861</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C158" t="s">
+        <v>735</v>
+      </c>
+      <c r="E158" s="47" t="s">
+        <v>862</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C159" t="s">
+        <v>735</v>
+      </c>
+      <c r="E159" s="47" t="s">
+        <v>863</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C160" t="s">
+        <v>735</v>
+      </c>
+      <c r="E160" s="47" t="s">
+        <v>864</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C161" t="s">
+        <v>735</v>
+      </c>
+      <c r="E161" s="47" t="s">
+        <v>865</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C162" t="s">
+        <v>735</v>
+      </c>
+      <c r="E162" s="47" t="s">
+        <v>866</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C163" t="s">
+        <v>735</v>
+      </c>
+      <c r="E163" t="s">
+        <v>867</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C164" t="s">
+        <v>735</v>
+      </c>
+      <c r="E164" t="s">
+        <v>869</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C165" t="s">
+        <v>735</v>
+      </c>
+      <c r="E165" t="s">
+        <v>871</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="32" t="s">
+        <v>860</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C166" t="s">
+        <v>735</v>
+      </c>
+      <c r="E166" t="s">
+        <v>873</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="32"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C169" t="s">
+        <v>918</v>
+      </c>
+      <c r="E169" s="44" t="s">
+        <v>855</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C170" t="s">
+        <v>918</v>
+      </c>
+      <c r="E170" t="s">
+        <v>856</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C171" t="s">
+        <v>918</v>
+      </c>
+      <c r="E171" s="47" t="s">
+        <v>785</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C174" t="s">
+        <v>918</v>
+      </c>
+      <c r="E174" t="s">
+        <v>821</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C175" t="s">
+        <v>918</v>
+      </c>
+      <c r="E175" t="s">
+        <v>824</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C176" t="s">
+        <v>918</v>
+      </c>
+      <c r="E176" t="s">
+        <v>822</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C177" t="s">
+        <v>918</v>
+      </c>
+      <c r="E177" t="s">
+        <v>823</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C178" t="s">
+        <v>918</v>
+      </c>
+      <c r="E178" t="s">
+        <v>825</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C179" t="s">
+        <v>918</v>
+      </c>
+      <c r="E179" t="s">
+        <v>826</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C180" t="s">
+        <v>918</v>
+      </c>
+      <c r="E180" t="s">
+        <v>827</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C181" t="s">
+        <v>918</v>
+      </c>
+      <c r="E181" t="s">
+        <v>832</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C182" t="s">
+        <v>918</v>
+      </c>
+      <c r="E182" t="s">
+        <v>829</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C183" t="s">
+        <v>918</v>
+      </c>
+      <c r="E183" t="s">
+        <v>828</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C184" t="s">
+        <v>918</v>
+      </c>
+      <c r="E184" s="44" t="s">
+        <v>830</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" s="32" t="s">
+        <v>885</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C185" t="s">
+        <v>918</v>
+      </c>
+      <c r="E185" s="44" t="s">
+        <v>831</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" s="32"/>
+      <c r="E186" s="44" t="s">
+        <v>785</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187" s="32"/>
+      <c r="E187" s="44"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C189" t="s">
+        <v>918</v>
+      </c>
+      <c r="E189" t="s">
+        <v>887</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C190" t="s">
+        <v>918</v>
+      </c>
+      <c r="E190" t="s">
+        <v>888</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C191" t="s">
+        <v>918</v>
+      </c>
+      <c r="E191" t="s">
+        <v>889</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C192" t="s">
+        <v>918</v>
+      </c>
+      <c r="E192" t="s">
+        <v>890</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="C193" t="s">
+        <v>918</v>
+      </c>
+      <c r="E193" t="s">
+        <v>897</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C194" t="s">
+        <v>918</v>
+      </c>
+      <c r="E194" t="s">
+        <v>896</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C195" t="s">
+        <v>918</v>
+      </c>
+      <c r="E195" t="s">
+        <v>891</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="C196" t="s">
+        <v>918</v>
+      </c>
+      <c r="E196" s="47" t="s">
+        <v>892</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C197" t="s">
+        <v>918</v>
+      </c>
+      <c r="E197" t="s">
+        <v>893</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198" s="32"/>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C200" t="s">
+        <v>673</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E200" t="s">
+        <v>911</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C201" t="s">
+        <v>673</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E201" t="s">
+        <v>910</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C202" t="s">
+        <v>673</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E202" s="47" t="s">
+        <v>909</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C203" t="s">
+        <v>673</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E203" t="s">
+        <v>908</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C204" t="s">
+        <v>673</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E204" t="s">
+        <v>907</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C205" t="s">
+        <v>673</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E205" t="s">
+        <v>906</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206" s="32"/>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207" s="32"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10971,8 +12702,32 @@
     <hyperlink ref="B84" r:id="rId31"/>
     <hyperlink ref="B86" r:id="rId32"/>
     <hyperlink ref="B88" r:id="rId33"/>
+    <hyperlink ref="B124" r:id="rId34"/>
+    <hyperlink ref="B125" r:id="rId35"/>
+    <hyperlink ref="B126" r:id="rId36"/>
+    <hyperlink ref="B128" r:id="rId37"/>
+    <hyperlink ref="B131" r:id="rId38"/>
+    <hyperlink ref="B127" r:id="rId39"/>
+    <hyperlink ref="B129" r:id="rId40"/>
+    <hyperlink ref="B130" r:id="rId41"/>
+    <hyperlink ref="F130" r:id="rId42"/>
+    <hyperlink ref="F129" r:id="rId43"/>
+    <hyperlink ref="F128" r:id="rId44"/>
+    <hyperlink ref="F125" r:id="rId45"/>
+    <hyperlink ref="F146" r:id="rId46"/>
+    <hyperlink ref="F151" r:id="rId47"/>
+    <hyperlink ref="F166" r:id="rId48"/>
+    <hyperlink ref="F162" r:id="rId49"/>
+    <hyperlink ref="F161" r:id="rId50"/>
+    <hyperlink ref="F159" r:id="rId51"/>
+    <hyperlink ref="F157" r:id="rId52"/>
+    <hyperlink ref="F156" r:id="rId53"/>
+    <hyperlink ref="F170" r:id="rId54"/>
+    <hyperlink ref="F185" r:id="rId55"/>
+    <hyperlink ref="F195" r:id="rId56"/>
+    <hyperlink ref="F196" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId34"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId58"/>
 </worksheet>
 </file>